--- a/report_2411.xlsx
+++ b/report_2411.xlsx
@@ -1048,7 +1048,6 @@
     <xf numFmtId="166" fontId="0" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="47" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
@@ -1061,6 +1060,7 @@
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="45" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="46" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="47" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="47" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="25" fillId="46" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -3788,13 +3788,13 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="87" t="inlineStr">
+      <c r="A24" s="76" t="inlineStr">
         <is>
           <t>升息概率</t>
         </is>
       </c>
       <c r="B24" s="85" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="C24" s="85" t="n">
         <v>100</v>
@@ -3890,94 +3890,94 @@
           <t>人民币</t>
         </is>
       </c>
-      <c r="B25" s="88" t="n">
+      <c r="B25" s="87" t="n">
+        <v>7.14</v>
+      </c>
+      <c r="C25" s="87" t="n">
+        <v>7.12</v>
+      </c>
+      <c r="D25" s="87" t="n">
         <v>7.13</v>
       </c>
-      <c r="C25" s="88" t="n">
+      <c r="E25" s="87" t="n">
+        <v>7.14</v>
+      </c>
+      <c r="F25" s="87" t="n">
+        <v>7.14</v>
+      </c>
+      <c r="G25" s="87" t="n">
+        <v>7.13</v>
+      </c>
+      <c r="H25" s="87" t="n">
+        <v>7.13</v>
+      </c>
+      <c r="I25" s="87" t="n">
+        <v>7.14</v>
+      </c>
+      <c r="J25" s="87" t="n">
+        <v>7.14</v>
+      </c>
+      <c r="K25" s="87" t="n">
+        <v>7.14</v>
+      </c>
+      <c r="L25" s="87" t="n">
         <v>7.12</v>
       </c>
-      <c r="D25" s="88" t="n">
+      <c r="M25" s="87" t="n">
+        <v>7.14</v>
+      </c>
+      <c r="N25" s="87" t="n">
         <v>7.13</v>
       </c>
-      <c r="E25" s="88" t="n">
+      <c r="O25" s="87" t="n">
         <v>7.14</v>
       </c>
-      <c r="F25" s="88" t="n">
-        <v>7.14</v>
-      </c>
-      <c r="G25" s="88" t="n">
-        <v>7.13</v>
-      </c>
-      <c r="H25" s="88" t="n">
-        <v>7.13</v>
-      </c>
-      <c r="I25" s="88" t="n">
-        <v>7.14</v>
-      </c>
-      <c r="J25" s="88" t="n">
-        <v>7.14</v>
-      </c>
-      <c r="K25" s="88" t="n">
-        <v>7.14</v>
-      </c>
-      <c r="L25" s="88" t="n">
-        <v>7.12</v>
-      </c>
-      <c r="M25" s="88" t="n">
-        <v>7.14</v>
-      </c>
-      <c r="N25" s="88" t="n">
-        <v>7.13</v>
-      </c>
-      <c r="O25" s="88" t="n">
-        <v>7.14</v>
-      </c>
-      <c r="P25" s="88" t="n">
+      <c r="P25" s="87" t="n">
         <v>7.09</v>
       </c>
-      <c r="Q25" s="88" t="n">
+      <c r="Q25" s="87" t="n">
         <v>7.07</v>
       </c>
-      <c r="R25" s="88" t="n">
+      <c r="R25" s="87" t="n">
         <v>7.08</v>
       </c>
-      <c r="S25" s="88" t="n">
+      <c r="S25" s="87" t="n">
         <v>7.09</v>
       </c>
-      <c r="T25" s="88" t="n">
+      <c r="T25" s="87" t="n">
         <v>7.07</v>
       </c>
-      <c r="U25" s="88" t="n">
+      <c r="U25" s="87" t="n">
         <v>7.01</v>
       </c>
-      <c r="V25" s="88" t="n">
+      <c r="V25" s="87" t="n">
         <v>6.98</v>
       </c>
-      <c r="W25" s="88" t="n">
+      <c r="W25" s="87" t="n">
         <v>6.98</v>
       </c>
-      <c r="X25" s="88" t="n">
+      <c r="X25" s="87" t="n">
         <v>7.03</v>
       </c>
-      <c r="Y25" s="88" t="n">
+      <c r="Y25" s="87" t="n">
         <v>7</v>
       </c>
-      <c r="Z25" s="88" t="n">
+      <c r="Z25" s="87" t="n">
         <v>7.06</v>
       </c>
-      <c r="AA25" s="88" t="n">
+      <c r="AA25" s="87" t="n">
         <v>7.04</v>
       </c>
-      <c r="AB25" s="88" t="n">
+      <c r="AB25" s="87" t="n">
         <v>7.07</v>
       </c>
-      <c r="AC25" s="88" t="n">
+      <c r="AC25" s="87" t="n">
         <v>7.1</v>
       </c>
-      <c r="AD25" s="88" t="n">
+      <c r="AD25" s="87" t="n">
         <v>7.1</v>
       </c>
-      <c r="AE25" s="88" t="n">
+      <c r="AE25" s="87" t="n">
         <v>7.12</v>
       </c>
     </row>
@@ -3987,94 +3987,94 @@
           <t>人民币涨跌幅</t>
         </is>
       </c>
-      <c r="B26" s="89" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="C26" s="89" t="n">
+      <c r="B26" s="88" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="C26" s="88" t="n">
         <v>-0.08</v>
       </c>
-      <c r="D26" s="88" t="n">
+      <c r="D26" s="87" t="n">
         <v>-0.21</v>
       </c>
-      <c r="E26" s="88" t="n">
+      <c r="E26" s="87" t="n">
         <v>-0.02</v>
       </c>
-      <c r="F26" s="88" t="n">
+      <c r="F26" s="87" t="n">
         <v>0.13</v>
       </c>
-      <c r="G26" s="88" t="n">
+      <c r="G26" s="87" t="n">
         <v>0.12</v>
       </c>
-      <c r="H26" s="88" t="n">
+      <c r="H26" s="87" t="n">
         <v>-0.14</v>
       </c>
-      <c r="I26" s="88" t="n">
+      <c r="I26" s="87" t="n">
         <v>-0.02</v>
       </c>
-      <c r="J26" s="88" t="n">
+      <c r="J26" s="87" t="n">
         <v>-0.01</v>
       </c>
-      <c r="K26" s="88" t="n">
+      <c r="K26" s="87" t="n">
         <v>0.3</v>
       </c>
-      <c r="L26" s="88" t="n">
+      <c r="L26" s="87" t="n">
         <v>-0.3</v>
       </c>
-      <c r="M26" s="88" t="n">
+      <c r="M26" s="87" t="n">
         <v>0.06</v>
       </c>
-      <c r="N26" s="88" t="n">
+      <c r="N26" s="87" t="n">
         <v>-0.07000000000000001</v>
       </c>
-      <c r="O26" s="88" t="n">
+      <c r="O26" s="87" t="n">
         <v>0.65</v>
       </c>
-      <c r="P26" s="88" t="n">
+      <c r="P26" s="87" t="n">
         <v>0.37</v>
       </c>
-      <c r="Q26" s="88" t="n">
+      <c r="Q26" s="87" t="n">
         <v>-0.23</v>
       </c>
-      <c r="R26" s="88" t="n">
+      <c r="R26" s="87" t="n">
         <v>-0.11</v>
       </c>
-      <c r="S26" s="88" t="n">
+      <c r="S26" s="87" t="n">
         <v>0.26</v>
       </c>
-      <c r="T26" s="88" t="n">
+      <c r="T26" s="87" t="n">
         <v>0.9</v>
       </c>
-      <c r="U26" s="88" t="n">
+      <c r="U26" s="87" t="n">
         <v>0.42</v>
       </c>
-      <c r="V26" s="88" t="n">
+      <c r="V26" s="87" t="n">
         <v>0.02</v>
       </c>
-      <c r="W26" s="88" t="n">
+      <c r="W26" s="87" t="n">
         <v>-0.79</v>
       </c>
-      <c r="X26" s="88" t="n">
+      <c r="X26" s="87" t="n">
         <v>0.49</v>
       </c>
-      <c r="Y26" s="88" t="n">
+      <c r="Y26" s="87" t="n">
         <v>-0.84</v>
       </c>
-      <c r="Z26" s="88" t="n">
+      <c r="Z26" s="87" t="n">
         <v>0.27</v>
       </c>
-      <c r="AA26" s="88" t="n">
+      <c r="AA26" s="87" t="n">
         <v>-0.44</v>
       </c>
-      <c r="AB26" s="88" t="n">
+      <c r="AB26" s="87" t="n">
         <v>-0.34</v>
       </c>
-      <c r="AC26" s="88" t="n">
+      <c r="AC26" s="87" t="n">
         <v>-0.02</v>
       </c>
-      <c r="AD26" s="88" t="n">
+      <c r="AD26" s="87" t="n">
         <v>-0.25</v>
       </c>
-      <c r="AE26" s="88" t="n">
+      <c r="AE26" s="87" t="n">
         <v>-0.15</v>
       </c>
     </row>
@@ -4084,94 +4084,94 @@
           <t>人民币20日涨跌幅</t>
         </is>
       </c>
-      <c r="B27" s="89" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="C27" s="89" t="n">
+      <c r="B27" s="88" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="C27" s="88" t="n">
         <v>2.03</v>
       </c>
-      <c r="D27" s="88" t="n">
+      <c r="D27" s="87" t="n">
         <v>1.3</v>
       </c>
-      <c r="E27" s="88" t="n">
+      <c r="E27" s="87" t="n">
         <v>2.02</v>
       </c>
-      <c r="F27" s="88" t="n">
+      <c r="F27" s="87" t="n">
         <v>1.19</v>
       </c>
-      <c r="G27" s="88" t="n">
+      <c r="G27" s="87" t="n">
         <v>1.32</v>
       </c>
-      <c r="H27" s="88" t="n">
+      <c r="H27" s="87" t="n">
         <v>0.76</v>
       </c>
-      <c r="I27" s="88" t="n">
+      <c r="I27" s="87" t="n">
         <v>0.55</v>
       </c>
-      <c r="J27" s="88" t="n">
+      <c r="J27" s="87" t="n">
         <v>0.55</v>
       </c>
-      <c r="K27" s="88" t="n">
+      <c r="K27" s="87" t="n">
         <v>0.31</v>
       </c>
-      <c r="L27" s="88" t="n">
+      <c r="L27" s="87" t="n">
         <v>-0.14</v>
       </c>
-      <c r="M27" s="88" t="n">
+      <c r="M27" s="87" t="n">
         <v>0.06</v>
       </c>
-      <c r="N27" s="88" t="n">
+      <c r="N27" s="87" t="n">
         <v>0.18</v>
       </c>
-      <c r="O27" s="88" t="n">
+      <c r="O27" s="87" t="n">
         <v>0.6899999999999999</v>
       </c>
-      <c r="P27" s="88" t="n">
+      <c r="P27" s="87" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="Q27" s="88" t="n">
+      <c r="Q27" s="87" t="n">
         <v>-0.54</v>
       </c>
-      <c r="R27" s="88" t="n">
+      <c r="R27" s="87" t="n">
         <v>-0.49</v>
       </c>
-      <c r="S27" s="88" t="n">
+      <c r="S27" s="87" t="n">
         <v>-0.35</v>
       </c>
-      <c r="T27" s="88" t="n">
+      <c r="T27" s="87" t="n">
         <v>-0.21</v>
       </c>
-      <c r="U27" s="88" t="n">
+      <c r="U27" s="87" t="n">
         <v>-1.11</v>
       </c>
-      <c r="V27" s="88" t="n">
+      <c r="V27" s="87" t="n">
         <v>-2.1</v>
       </c>
-      <c r="W27" s="88" t="n">
+      <c r="W27" s="87" t="n">
         <v>-2</v>
       </c>
-      <c r="X27" s="88" t="n">
+      <c r="X27" s="87" t="n">
         <v>-1.27</v>
       </c>
-      <c r="Y27" s="88" t="n">
+      <c r="Y27" s="87" t="n">
         <v>-1.61</v>
       </c>
-      <c r="Z27" s="88" t="n">
+      <c r="Z27" s="87" t="n">
         <v>-1.2</v>
       </c>
-      <c r="AA27" s="88" t="n">
+      <c r="AA27" s="87" t="n">
         <v>-1.26</v>
       </c>
-      <c r="AB27" s="88" t="n">
+      <c r="AB27" s="87" t="n">
         <v>-0.59</v>
       </c>
-      <c r="AC27" s="88" t="n">
+      <c r="AC27" s="87" t="n">
         <v>-0.47</v>
       </c>
-      <c r="AD27" s="88" t="n">
+      <c r="AD27" s="87" t="n">
         <v>-0.88</v>
       </c>
-      <c r="AE27" s="88" t="n">
+      <c r="AE27" s="87" t="n">
         <v>-0.93</v>
       </c>
     </row>
@@ -4375,94 +4375,94 @@
           <t>多空比</t>
         </is>
       </c>
-      <c r="B30" s="90" t="n">
+      <c r="B30" s="89" t="n">
         <v>46.71</v>
       </c>
-      <c r="C30" s="90" t="n">
+      <c r="C30" s="89" t="n">
         <v>46.84</v>
       </c>
-      <c r="D30" s="90" t="n">
+      <c r="D30" s="89" t="n">
         <v>46.58</v>
       </c>
-      <c r="E30" s="90" t="n">
+      <c r="E30" s="89" t="n">
         <v>46.54</v>
       </c>
-      <c r="F30" s="90" t="n">
+      <c r="F30" s="89" t="n">
         <v>46.29</v>
       </c>
-      <c r="G30" s="90" t="n">
+      <c r="G30" s="89" t="n">
         <v>46.42</v>
       </c>
-      <c r="H30" s="90" t="n">
+      <c r="H30" s="89" t="n">
         <v>46.29</v>
       </c>
-      <c r="I30" s="90" t="n">
+      <c r="I30" s="89" t="n">
         <v>46.4</v>
       </c>
-      <c r="J30" s="90" t="n">
+      <c r="J30" s="89" t="n">
         <v>46.28</v>
       </c>
-      <c r="K30" s="90" t="n">
+      <c r="K30" s="89" t="n">
         <v>46.28</v>
       </c>
-      <c r="L30" s="90" t="n">
+      <c r="L30" s="89" t="n">
         <v>46.33</v>
       </c>
-      <c r="M30" s="90" t="n">
+      <c r="M30" s="89" t="n">
         <v>46.57</v>
       </c>
-      <c r="N30" s="90" t="n">
+      <c r="N30" s="89" t="n">
         <v>46.24</v>
       </c>
-      <c r="O30" s="90" t="n">
+      <c r="O30" s="89" t="n">
         <v>46.29</v>
       </c>
-      <c r="P30" s="90" t="n">
+      <c r="P30" s="89" t="n">
         <v>46.19</v>
       </c>
-      <c r="Q30" s="90" t="n">
+      <c r="Q30" s="89" t="n">
         <v>46.21</v>
       </c>
-      <c r="R30" s="90" t="n">
+      <c r="R30" s="89" t="n">
         <v>46.19</v>
       </c>
-      <c r="S30" s="90" t="n">
+      <c r="S30" s="89" t="n">
         <v>46.16</v>
       </c>
-      <c r="T30" s="90" t="n">
+      <c r="T30" s="89" t="n">
         <v>45.91</v>
       </c>
-      <c r="U30" s="90" t="n">
+      <c r="U30" s="89" t="n">
         <v>46.49</v>
       </c>
-      <c r="V30" s="90" t="n">
+      <c r="V30" s="89" t="n">
         <v>46.8</v>
       </c>
-      <c r="W30" s="90" t="n">
+      <c r="W30" s="89" t="n">
         <v>46.99</v>
       </c>
-      <c r="X30" s="90" t="n">
+      <c r="X30" s="89" t="n">
         <v>47.26</v>
       </c>
-      <c r="Y30" s="90" t="n">
+      <c r="Y30" s="89" t="n">
         <v>47.47</v>
       </c>
-      <c r="Z30" s="90" t="n">
+      <c r="Z30" s="89" t="n">
         <v>47.52</v>
       </c>
-      <c r="AA30" s="90" t="n">
+      <c r="AA30" s="89" t="n">
         <v>47.5</v>
       </c>
-      <c r="AB30" s="90" t="n">
+      <c r="AB30" s="89" t="n">
         <v>47.39</v>
       </c>
-      <c r="AC30" s="90" t="n">
+      <c r="AC30" s="89" t="n">
         <v>47.54</v>
       </c>
-      <c r="AD30" s="90" t="n">
+      <c r="AD30" s="89" t="n">
         <v>47.31</v>
       </c>
-      <c r="AE30" s="90" t="n">
+      <c r="AE30" s="89" t="n">
         <v>47.24</v>
       </c>
     </row>
@@ -5340,16 +5340,16 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="91" t="inlineStr">
+      <c r="A41" s="90" t="inlineStr">
         <is>
           <t>今日买报：</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="91" t="inlineStr">
-        <is>
-          <t>今日卖报：升息概率:100.0&gt;=100.0</t>
+      <c r="A42" s="90" t="inlineStr">
+        <is>
+          <t>今日卖报：</t>
         </is>
       </c>
     </row>
@@ -6497,157 +6497,157 @@
           <t>sh:EIDE</t>
         </is>
       </c>
-      <c r="B2" s="92" t="inlineStr">
+      <c r="B2" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="C2" s="92" t="inlineStr">
+      <c r="C2" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="D2" s="92" t="inlineStr">
+      <c r="D2" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="E2" s="92" t="inlineStr">
+      <c r="E2" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="F2" s="92" t="inlineStr">
+      <c r="F2" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="G2" s="92" t="inlineStr">
+      <c r="G2" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="H2" s="92" t="inlineStr">
+      <c r="H2" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="I2" s="92" t="inlineStr">
+      <c r="I2" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="J2" s="92" t="inlineStr">
+      <c r="J2" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="K2" s="92" t="inlineStr">
+      <c r="K2" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="L2" s="92" t="inlineStr">
+      <c r="L2" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="M2" s="92" t="inlineStr">
+      <c r="M2" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="N2" s="92" t="inlineStr">
+      <c r="N2" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="O2" s="92" t="inlineStr">
+      <c r="O2" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="P2" s="92" t="inlineStr">
+      <c r="P2" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="Q2" s="92" t="inlineStr">
+      <c r="Q2" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="R2" s="92" t="inlineStr">
+      <c r="R2" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="S2" s="92" t="inlineStr">
+      <c r="S2" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="T2" s="92" t="inlineStr">
+      <c r="T2" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="U2" s="92" t="inlineStr">
+      <c r="U2" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="V2" s="92" t="inlineStr">
+      <c r="V2" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="W2" s="93" t="inlineStr">
+      <c r="W2" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="X2" s="93" t="inlineStr">
+      <c r="X2" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="Y2" s="93" t="inlineStr">
+      <c r="Y2" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="Z2" s="93" t="inlineStr">
+      <c r="Z2" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="AA2" s="93" t="inlineStr">
+      <c r="AA2" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="AB2" s="93" t="inlineStr">
+      <c r="AB2" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="AC2" s="93" t="inlineStr">
+      <c r="AC2" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="AD2" s="93" t="inlineStr">
+      <c r="AD2" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="AE2" s="92" t="n">
+      <c r="AE2" s="91" t="n">
         <v/>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="87" t="inlineStr">
+      <c r="A3" s="93" t="inlineStr">
         <is>
           <t>sh:RNG60</t>
         </is>
@@ -6948,152 +6948,152 @@
           <t>green</t>
         </is>
       </c>
-      <c r="C6" s="92" t="inlineStr">
+      <c r="C6" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="D6" s="92" t="inlineStr">
+      <c r="D6" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="E6" s="92" t="inlineStr">
+      <c r="E6" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="F6" s="92" t="inlineStr">
+      <c r="F6" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="G6" s="92" t="inlineStr">
+      <c r="G6" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="H6" s="92" t="inlineStr">
+      <c r="H6" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="I6" s="92" t="inlineStr">
+      <c r="I6" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="J6" s="92" t="inlineStr">
+      <c r="J6" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="K6" s="92" t="inlineStr">
+      <c r="K6" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="L6" s="93" t="inlineStr">
+      <c r="L6" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="M6" s="93" t="inlineStr">
+      <c r="M6" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="N6" s="93" t="inlineStr">
+      <c r="N6" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="O6" s="92" t="inlineStr">
+      <c r="O6" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="P6" s="92" t="inlineStr">
+      <c r="P6" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="Q6" s="92" t="inlineStr">
+      <c r="Q6" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="R6" s="92" t="inlineStr">
+      <c r="R6" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="S6" s="92" t="inlineStr">
+      <c r="S6" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="T6" s="92" t="inlineStr">
+      <c r="T6" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="U6" s="92" t="inlineStr">
+      <c r="U6" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="V6" s="93" t="inlineStr">
+      <c r="V6" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="W6" s="93" t="inlineStr">
+      <c r="W6" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="X6" s="93" t="inlineStr">
+      <c r="X6" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="Y6" s="93" t="inlineStr">
+      <c r="Y6" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="Z6" s="93" t="inlineStr">
+      <c r="Z6" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="AA6" s="93" t="inlineStr">
+      <c r="AA6" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="AB6" s="93" t="inlineStr">
+      <c r="AB6" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="AC6" s="93" t="inlineStr">
+      <c r="AC6" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="AD6" s="93" t="inlineStr">
+      <c r="AD6" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="AE6" s="92" t="n">
+      <c r="AE6" s="91" t="n">
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="87" t="inlineStr">
+      <c r="A7" s="93" t="inlineStr">
         <is>
           <t>kc:RNG60</t>
         </is>
@@ -7394,152 +7394,152 @@
           <t>green</t>
         </is>
       </c>
-      <c r="C10" s="92" t="inlineStr">
+      <c r="C10" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="D10" s="92" t="inlineStr">
+      <c r="D10" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="E10" s="92" t="inlineStr">
+      <c r="E10" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="F10" s="92" t="inlineStr">
+      <c r="F10" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="G10" s="92" t="inlineStr">
+      <c r="G10" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="H10" s="92" t="inlineStr">
+      <c r="H10" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="I10" s="92" t="inlineStr">
+      <c r="I10" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="J10" s="92" t="inlineStr">
+      <c r="J10" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="K10" s="92" t="inlineStr">
+      <c r="K10" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="L10" s="92" t="inlineStr">
+      <c r="L10" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="M10" s="93" t="inlineStr">
+      <c r="M10" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="N10" s="93" t="inlineStr">
+      <c r="N10" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="O10" s="92" t="inlineStr">
+      <c r="O10" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="P10" s="92" t="inlineStr">
+      <c r="P10" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="Q10" s="92" t="inlineStr">
+      <c r="Q10" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="R10" s="92" t="inlineStr">
+      <c r="R10" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="S10" s="92" t="inlineStr">
+      <c r="S10" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="T10" s="92" t="inlineStr">
+      <c r="T10" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="U10" s="92" t="inlineStr">
+      <c r="U10" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="V10" s="93" t="inlineStr">
+      <c r="V10" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="W10" s="93" t="inlineStr">
+      <c r="W10" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="X10" s="93" t="inlineStr">
+      <c r="X10" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="Y10" s="93" t="inlineStr">
+      <c r="Y10" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="Z10" s="93" t="inlineStr">
+      <c r="Z10" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="AA10" s="93" t="inlineStr">
+      <c r="AA10" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="AB10" s="93" t="inlineStr">
+      <c r="AB10" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="AC10" s="93" t="inlineStr">
+      <c r="AC10" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="AD10" s="93" t="inlineStr">
+      <c r="AD10" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="AE10" s="92" t="n">
+      <c r="AE10" s="91" t="n">
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="87" t="inlineStr">
+      <c r="A11" s="93" t="inlineStr">
         <is>
           <t>cy:RNG60</t>
         </is>
@@ -7835,7 +7835,7 @@
           <t>hk50:EIDE</t>
         </is>
       </c>
-      <c r="B14" s="92" t="inlineStr">
+      <c r="B14" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
@@ -7850,22 +7850,22 @@
           <t>green</t>
         </is>
       </c>
-      <c r="E14" s="93" t="inlineStr">
+      <c r="E14" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="F14" s="93" t="inlineStr">
+      <c r="F14" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="G14" s="92" t="inlineStr">
+      <c r="G14" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="H14" s="92" t="inlineStr">
+      <c r="H14" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
@@ -7875,7 +7875,7 @@
           <t>green</t>
         </is>
       </c>
-      <c r="J14" s="93" t="inlineStr">
+      <c r="J14" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
@@ -7890,12 +7890,12 @@
           <t>green</t>
         </is>
       </c>
-      <c r="M14" s="93" t="inlineStr">
+      <c r="M14" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="N14" s="93" t="inlineStr">
+      <c r="N14" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
@@ -7915,22 +7915,22 @@
           <t>green</t>
         </is>
       </c>
-      <c r="R14" s="92" t="inlineStr">
+      <c r="R14" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="S14" s="92" t="inlineStr">
+      <c r="S14" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="T14" s="92" t="inlineStr">
+      <c r="T14" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="U14" s="92" t="inlineStr">
+      <c r="U14" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
@@ -7940,52 +7940,52 @@
           <t>green</t>
         </is>
       </c>
-      <c r="W14" s="92" t="inlineStr">
+      <c r="W14" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="X14" s="93" t="inlineStr">
+      <c r="X14" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="Y14" s="93" t="inlineStr">
+      <c r="Y14" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="Z14" s="93" t="inlineStr">
+      <c r="Z14" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="AA14" s="93" t="inlineStr">
+      <c r="AA14" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="AB14" s="93" t="inlineStr">
+      <c r="AB14" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="AC14" s="93" t="inlineStr">
+      <c r="AC14" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="AD14" s="93" t="inlineStr">
+      <c r="AD14" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="AE14" s="92" t="n">
+      <c r="AE14" s="91" t="n">
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="87" t="inlineStr">
+      <c r="A15" s="93" t="inlineStr">
         <is>
           <t>hk50:RNG60</t>
         </is>
@@ -8296,12 +8296,12 @@
           <t>green</t>
         </is>
       </c>
-      <c r="E18" s="93" t="inlineStr">
+      <c r="E18" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="F18" s="92" t="inlineStr">
+      <c r="F18" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
@@ -8326,67 +8326,67 @@
           <t>green</t>
         </is>
       </c>
-      <c r="K18" s="92" t="inlineStr">
+      <c r="K18" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="L18" s="92" t="inlineStr">
+      <c r="L18" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="M18" s="93" t="inlineStr">
+      <c r="M18" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="N18" s="93" t="inlineStr">
+      <c r="N18" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="O18" s="92" t="inlineStr">
+      <c r="O18" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="P18" s="93" t="inlineStr">
+      <c r="P18" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="Q18" s="92" t="inlineStr">
+      <c r="Q18" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="R18" s="93" t="inlineStr">
+      <c r="R18" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="S18" s="93" t="inlineStr">
+      <c r="S18" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="T18" s="93" t="inlineStr">
+      <c r="T18" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="U18" s="93" t="inlineStr">
+      <c r="U18" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="V18" s="93" t="inlineStr">
+      <c r="V18" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="W18" s="93" t="inlineStr">
+      <c r="W18" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
@@ -8396,37 +8396,37 @@
           <t>green</t>
         </is>
       </c>
-      <c r="Y18" s="93" t="inlineStr">
+      <c r="Y18" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="Z18" s="93" t="inlineStr">
+      <c r="Z18" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="AA18" s="92" t="inlineStr">
+      <c r="AA18" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="AB18" s="92" t="inlineStr">
+      <c r="AB18" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="AC18" s="92" t="inlineStr">
+      <c r="AC18" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="AD18" s="92" t="inlineStr">
+      <c r="AD18" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="AE18" s="92" t="n">
+      <c r="AE18" s="91" t="n">
         <v/>
       </c>
     </row>
@@ -8437,7 +8437,7 @@
         </is>
       </c>
       <c r="B19" s="94" t="n">
-        <v>9.73</v>
+        <v>7.7</v>
       </c>
       <c r="C19" s="94" t="n">
         <v>9.73</v>
@@ -8534,7 +8534,7 @@
         </is>
       </c>
       <c r="B20" s="94" t="n">
-        <v>9.24</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="C20" s="94" t="n">
         <v>9.24</v>
@@ -8625,13 +8625,13 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="96" t="inlineStr">
+      <c r="A21" s="76" t="inlineStr">
         <is>
           <t>us500:RS2</t>
         </is>
       </c>
       <c r="B21" s="94" t="n">
-        <v>3.83</v>
+        <v>30.2</v>
       </c>
       <c r="C21" s="94" t="n">
         <v>3.83</v>
@@ -8727,152 +8727,152 @@
           <t>us30:EIDE</t>
         </is>
       </c>
-      <c r="B22" s="95" t="inlineStr">
+      <c r="B22" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="C22" s="95" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="C22" s="95" t="inlineStr">
+      <c r="D22" s="95" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="D22" s="95" t="inlineStr">
+      <c r="E22" s="95" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="E22" s="95" t="inlineStr">
+      <c r="F22" s="95" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="F22" s="95" t="inlineStr">
+      <c r="G22" s="95" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="G22" s="95" t="inlineStr">
+      <c r="H22" s="95" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="H22" s="95" t="inlineStr">
+      <c r="I22" s="95" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="I22" s="95" t="inlineStr">
+      <c r="J22" s="95" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="J22" s="95" t="inlineStr">
+      <c r="K22" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="L22" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="M22" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="N22" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="O22" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="P22" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="Q22" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="R22" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="S22" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="T22" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="U22" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="V22" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="W22" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="X22" s="95" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="K22" s="92" t="inlineStr">
+      <c r="Y22" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="Z22" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="AA22" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="L22" s="92" t="inlineStr">
+      <c r="AB22" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="M22" s="93" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="N22" s="93" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="O22" s="93" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="P22" s="93" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="Q22" s="92" t="inlineStr">
+      <c r="AC22" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="R22" s="93" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="S22" s="93" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="T22" s="93" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="U22" s="93" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="V22" s="93" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="W22" s="92" t="inlineStr">
+      <c r="AD22" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="X22" s="95" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="Y22" s="93" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="Z22" s="93" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="AA22" s="92" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="AB22" s="92" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="AC22" s="92" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="AD22" s="92" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="AE22" s="92" t="n">
+      <c r="AE22" s="91" t="n">
         <v/>
       </c>
     </row>
@@ -8883,7 +8883,7 @@
         </is>
       </c>
       <c r="B23" s="94" t="n">
-        <v>7.74</v>
+        <v>6.61</v>
       </c>
       <c r="C23" s="94" t="n">
         <v>7.74</v>
@@ -8980,7 +8980,7 @@
         </is>
       </c>
       <c r="B24" s="94" t="n">
-        <v>5.7</v>
+        <v>6.65</v>
       </c>
       <c r="C24" s="94" t="n">
         <v>5.7</v>
@@ -9071,13 +9071,13 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="96" t="inlineStr">
+      <c r="A25" s="76" t="inlineStr">
         <is>
           <t>us30:RS3</t>
         </is>
       </c>
       <c r="B25" s="94" t="n">
-        <v>12.74</v>
+        <v>45.44</v>
       </c>
       <c r="C25" s="94" t="n">
         <v>12.74</v>
@@ -9183,32 +9183,32 @@
           <t>green</t>
         </is>
       </c>
-      <c r="D26" s="92" t="inlineStr">
+      <c r="D26" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="E26" s="93" t="inlineStr">
+      <c r="E26" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="F26" s="93" t="inlineStr">
+      <c r="F26" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="G26" s="93" t="inlineStr">
+      <c r="G26" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="H26" s="93" t="inlineStr">
+      <c r="H26" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="I26" s="92" t="inlineStr">
+      <c r="I26" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
@@ -9218,67 +9218,67 @@
           <t>green</t>
         </is>
       </c>
-      <c r="K26" s="93" t="inlineStr">
+      <c r="K26" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="L26" s="93" t="inlineStr">
+      <c r="L26" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="M26" s="93" t="inlineStr">
+      <c r="M26" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="N26" s="93" t="inlineStr">
+      <c r="N26" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="O26" s="92" t="inlineStr">
+      <c r="O26" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="P26" s="92" t="inlineStr">
+      <c r="P26" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="Q26" s="92" t="inlineStr">
+      <c r="Q26" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="R26" s="93" t="inlineStr">
+      <c r="R26" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="S26" s="93" t="inlineStr">
+      <c r="S26" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="T26" s="93" t="inlineStr">
+      <c r="T26" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="U26" s="93" t="inlineStr">
+      <c r="U26" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="V26" s="93" t="inlineStr">
+      <c r="V26" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="W26" s="93" t="inlineStr">
+      <c r="W26" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
@@ -9288,37 +9288,37 @@
           <t>green</t>
         </is>
       </c>
-      <c r="Y26" s="93" t="inlineStr">
+      <c r="Y26" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="Z26" s="93" t="inlineStr">
+      <c r="Z26" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="AA26" s="92" t="inlineStr">
+      <c r="AA26" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="AB26" s="92" t="inlineStr">
+      <c r="AB26" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="AC26" s="92" t="inlineStr">
+      <c r="AC26" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="AD26" s="92" t="inlineStr">
+      <c r="AD26" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="AE26" s="92" t="n">
+      <c r="AE26" s="91" t="n">
         <v/>
       </c>
     </row>
@@ -9329,7 +9329,7 @@
         </is>
       </c>
       <c r="B27" s="94" t="n">
-        <v>11.73</v>
+        <v>9.48</v>
       </c>
       <c r="C27" s="94" t="n">
         <v>11.73</v>
@@ -9426,7 +9426,7 @@
         </is>
       </c>
       <c r="B28" s="94" t="n">
-        <v>10.74</v>
+        <v>11.3</v>
       </c>
       <c r="C28" s="94" t="n">
         <v>10.74</v>
@@ -9523,7 +9523,7 @@
         </is>
       </c>
       <c r="B29" s="94" t="n">
-        <v>8.65</v>
+        <v>37.61</v>
       </c>
       <c r="C29" s="94" t="n">
         <v>8.65</v>
@@ -9624,22 +9624,22 @@
           <t>green</t>
         </is>
       </c>
-      <c r="C30" s="93" t="inlineStr">
+      <c r="C30" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="D30" s="93" t="inlineStr">
+      <c r="D30" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="E30" s="93" t="inlineStr">
+      <c r="E30" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="F30" s="93" t="inlineStr">
+      <c r="F30" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
@@ -9674,12 +9674,12 @@
           <t>green</t>
         </is>
       </c>
-      <c r="M30" s="92" t="inlineStr">
+      <c r="M30" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="N30" s="92" t="inlineStr">
+      <c r="N30" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
@@ -9689,62 +9689,62 @@
           <t>green</t>
         </is>
       </c>
-      <c r="P30" s="92" t="inlineStr">
+      <c r="P30" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="Q30" s="93" t="inlineStr">
+      <c r="Q30" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="R30" s="93" t="inlineStr">
+      <c r="R30" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="S30" s="93" t="inlineStr">
+      <c r="S30" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="T30" s="93" t="inlineStr">
+      <c r="T30" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="U30" s="92" t="inlineStr">
+      <c r="U30" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="V30" s="92" t="inlineStr">
+      <c r="V30" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="W30" s="92" t="inlineStr">
+      <c r="W30" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="X30" s="93" t="inlineStr">
+      <c r="X30" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="Y30" s="92" t="inlineStr">
+      <c r="Y30" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="Z30" s="92" t="inlineStr">
+      <c r="Z30" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="AA30" s="92" t="inlineStr">
+      <c r="AA30" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
@@ -9754,17 +9754,17 @@
           <t>green</t>
         </is>
       </c>
-      <c r="AC30" s="92" t="inlineStr">
+      <c r="AC30" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="AD30" s="92" t="inlineStr">
+      <c r="AD30" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="AE30" s="92" t="n">
+      <c r="AE30" s="91" t="n">
         <v/>
       </c>
     </row>
@@ -10070,17 +10070,17 @@
           <t>green</t>
         </is>
       </c>
-      <c r="C34" s="92" t="inlineStr">
+      <c r="C34" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="D34" s="92" t="inlineStr">
+      <c r="D34" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="E34" s="92" t="inlineStr">
+      <c r="E34" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
@@ -10120,17 +10120,17 @@
           <t>green</t>
         </is>
       </c>
-      <c r="M34" s="93" t="inlineStr">
+      <c r="M34" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="N34" s="93" t="inlineStr">
+      <c r="N34" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="O34" s="93" t="inlineStr">
+      <c r="O34" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
@@ -10140,32 +10140,32 @@
           <t>green</t>
         </is>
       </c>
-      <c r="Q34" s="92" t="inlineStr">
+      <c r="Q34" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="R34" s="93" t="inlineStr">
+      <c r="R34" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="S34" s="93" t="inlineStr">
+      <c r="S34" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="T34" s="93" t="inlineStr">
+      <c r="T34" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="U34" s="93" t="inlineStr">
+      <c r="U34" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="V34" s="93" t="inlineStr">
+      <c r="V34" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
@@ -10195,22 +10195,22 @@
           <t>green</t>
         </is>
       </c>
-      <c r="AB34" s="92" t="inlineStr">
+      <c r="AB34" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="AC34" s="92" t="inlineStr">
+      <c r="AC34" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="AD34" s="92" t="inlineStr">
+      <c r="AD34" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="AE34" s="92" t="n">
+      <c r="AE34" s="91" t="n">
         <v/>
       </c>
     </row>
@@ -10511,152 +10511,152 @@
           <t>sensex:EIDE</t>
         </is>
       </c>
-      <c r="B38" s="95" t="inlineStr">
+      <c r="B38" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="C38" s="95" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="C38" s="95" t="inlineStr">
+      <c r="D38" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="E38" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="F38" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="G38" s="95" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="D38" s="92" t="inlineStr">
+      <c r="H38" s="95" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="I38" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="E38" s="92" t="inlineStr">
+      <c r="J38" s="95" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="K38" s="95" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="L38" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="F38" s="92" t="inlineStr">
+      <c r="M38" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="G38" s="95" t="inlineStr">
+      <c r="N38" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="O38" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="P38" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="Q38" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="R38" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="S38" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="T38" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="U38" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="V38" s="95" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="H38" s="95" t="inlineStr">
+      <c r="W38" s="95" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="I38" s="92" t="inlineStr">
+      <c r="X38" s="95" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="Y38" s="95" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="Z38" s="95" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="AA38" s="95" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="AB38" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="J38" s="95" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="K38" s="95" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="L38" s="92" t="inlineStr">
+      <c r="AC38" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="M38" s="92" t="inlineStr">
+      <c r="AD38" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="N38" s="92" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="O38" s="92" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="P38" s="92" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="Q38" s="92" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="R38" s="92" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="S38" s="92" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="T38" s="92" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="U38" s="92" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="V38" s="95" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="W38" s="95" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="X38" s="95" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="Y38" s="95" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="Z38" s="95" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="AA38" s="95" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="AB38" s="92" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="AC38" s="92" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="AD38" s="92" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="AE38" s="92" t="n">
+      <c r="AE38" s="91" t="n">
         <v/>
       </c>
     </row>
@@ -10667,7 +10667,7 @@
         </is>
       </c>
       <c r="B39" s="94" t="n">
-        <v>-0.1</v>
+        <v>1.06</v>
       </c>
       <c r="C39" s="94" t="n">
         <v>-0.1</v>
@@ -10764,7 +10764,7 @@
         </is>
       </c>
       <c r="B40" s="94" t="n">
-        <v>9.09</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="C40" s="94" t="n">
         <v>9.09</v>
@@ -10861,7 +10861,7 @@
         </is>
       </c>
       <c r="B41" s="94" t="n">
-        <v>31.56</v>
+        <v>36.99</v>
       </c>
       <c r="C41" s="94" t="n">
         <v>31.56</v>
@@ -10957,152 +10957,152 @@
           <t>fr40:EIDE</t>
         </is>
       </c>
-      <c r="B42" s="95" t="inlineStr">
+      <c r="B42" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="C42" s="95" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="C42" s="95" t="inlineStr">
+      <c r="D42" s="95" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="D42" s="95" t="inlineStr">
+      <c r="E42" s="95" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="E42" s="95" t="inlineStr">
+      <c r="F42" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="G42" s="95" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="F42" s="93" t="inlineStr">
+      <c r="H42" s="95" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="I42" s="95" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="J42" s="95" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="K42" s="95" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="L42" s="95" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="M42" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="G42" s="95" t="inlineStr">
+      <c r="N42" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="O42" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="P42" s="95" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="H42" s="95" t="inlineStr">
+      <c r="Q42" s="95" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="I42" s="95" t="inlineStr">
+      <c r="R42" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="S42" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="T42" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="U42" s="95" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="J42" s="95" t="inlineStr">
+      <c r="V42" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+      <c r="W42" s="95" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="K42" s="95" t="inlineStr">
+      <c r="X42" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+      <c r="Y42" s="95" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="L42" s="95" t="inlineStr">
+      <c r="Z42" s="95" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="M42" s="93" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="N42" s="93" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="O42" s="93" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="P42" s="95" t="inlineStr">
+      <c r="AA42" s="95" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="Q42" s="95" t="inlineStr">
+      <c r="AB42" s="95" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="R42" s="93" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="S42" s="93" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="T42" s="93" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="U42" s="95" t="inlineStr">
+      <c r="AC42" s="95" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="V42" s="92" t="inlineStr">
+      <c r="AD42" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="W42" s="95" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="X42" s="93" t="inlineStr">
-        <is>
-          <t>red</t>
-        </is>
-      </c>
-      <c r="Y42" s="95" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="Z42" s="95" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="AA42" s="95" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="AB42" s="95" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="AC42" s="95" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="AD42" s="92" t="inlineStr">
-        <is>
-          <t>blue</t>
-        </is>
-      </c>
-      <c r="AE42" s="92" t="n">
+      <c r="AE42" s="91" t="n">
         <v/>
       </c>
     </row>
@@ -11113,7 +11113,7 @@
         </is>
       </c>
       <c r="B43" s="94" t="n">
-        <v>1.66</v>
+        <v>1.92</v>
       </c>
       <c r="C43" s="94" t="n">
         <v>1.42</v>
@@ -11210,7 +11210,7 @@
         </is>
       </c>
       <c r="B44" s="94" t="n">
-        <v>-9.52</v>
+        <v>-9.289999999999999</v>
       </c>
       <c r="C44" s="94" t="n">
         <v>-10.24</v>
@@ -11307,7 +11307,7 @@
         </is>
       </c>
       <c r="B45" s="94" t="n">
-        <v>32.68</v>
+        <v>37.41</v>
       </c>
       <c r="C45" s="94" t="n">
         <v>20.06</v>
@@ -11418,27 +11418,27 @@
           <t>green</t>
         </is>
       </c>
-      <c r="E46" s="92" t="inlineStr">
+      <c r="E46" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="F46" s="93" t="inlineStr">
+      <c r="F46" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="G46" s="92" t="inlineStr">
+      <c r="G46" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="H46" s="92" t="inlineStr">
+      <c r="H46" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="I46" s="92" t="inlineStr">
+      <c r="I46" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
@@ -11448,82 +11448,82 @@
           <t>green</t>
         </is>
       </c>
-      <c r="K46" s="92" t="inlineStr">
+      <c r="K46" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="L46" s="92" t="inlineStr">
+      <c r="L46" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="M46" s="93" t="inlineStr">
+      <c r="M46" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="N46" s="93" t="inlineStr">
+      <c r="N46" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="O46" s="93" t="inlineStr">
+      <c r="O46" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="P46" s="92" t="inlineStr">
+      <c r="P46" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="Q46" s="93" t="inlineStr">
+      <c r="Q46" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="R46" s="93" t="inlineStr">
+      <c r="R46" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="S46" s="93" t="inlineStr">
+      <c r="S46" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="T46" s="93" t="inlineStr">
+      <c r="T46" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="U46" s="92" t="inlineStr">
+      <c r="U46" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="V46" s="93" t="inlineStr">
+      <c r="V46" s="92" t="inlineStr">
         <is>
           <t>red</t>
         </is>
       </c>
-      <c r="W46" s="92" t="inlineStr">
+      <c r="W46" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="X46" s="92" t="inlineStr">
+      <c r="X46" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="Y46" s="92" t="inlineStr">
+      <c r="Y46" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="Z46" s="92" t="inlineStr">
+      <c r="Z46" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
@@ -11533,22 +11533,22 @@
           <t>green</t>
         </is>
       </c>
-      <c r="AB46" s="92" t="inlineStr">
+      <c r="AB46" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="AC46" s="92" t="inlineStr">
+      <c r="AC46" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="AD46" s="92" t="inlineStr">
+      <c r="AD46" s="91" t="inlineStr">
         <is>
           <t>blue</t>
         </is>
       </c>
-      <c r="AE46" s="92" t="n">
+      <c r="AE46" s="91" t="n">
         <v/>
       </c>
     </row>
@@ -11559,7 +11559,7 @@
         </is>
       </c>
       <c r="B47" s="94" t="n">
-        <v>8.130000000000001</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="C47" s="94" t="n">
         <v>7.9</v>
@@ -11656,7 +11656,7 @@
         </is>
       </c>
       <c r="B48" s="94" t="n">
-        <v>2.45</v>
+        <v>2.94</v>
       </c>
       <c r="C48" s="94" t="n">
         <v>1.81</v>
@@ -11753,7 +11753,7 @@
         </is>
       </c>
       <c r="B49" s="94" t="n">
-        <v>34.82</v>
+        <v>42.99</v>
       </c>
       <c r="C49" s="94" t="n">
         <v>24.69</v>
@@ -11844,14 +11844,14 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="91" t="inlineStr">
-        <is>
-          <t>今日买报：us500:RS2:3.83&lt;=22;us30:RS3:12.74&lt;=25;ixic:RS2:8.65&lt;=38;sensex:RS10:31.56&lt;=39</t>
+      <c r="A51" s="90" t="inlineStr">
+        <is>
+          <t>今日买报：ixic:RS2:37.61&lt;=38;sensex:RS10:36.99&lt;=39</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="91" t="inlineStr">
+      <c r="A52" s="90" t="inlineStr">
         <is>
           <t>今日卖报：sh:RNG60:11.34&gt;=10;kc:RNG60:26.42&gt;=25;cy:RNG60:25.8&gt;=25;hk50:RNG60:22.81&gt;=15</t>
         </is>

--- a/report_2411.xlsx
+++ b/report_2411.xlsx
@@ -3891,7 +3891,7 @@
         </is>
       </c>
       <c r="B25" s="87" t="n">
-        <v>7.1</v>
+        <v>7.11</v>
       </c>
       <c r="C25" s="87" t="n">
         <v>7.14</v>
@@ -3988,7 +3988,7 @@
         </is>
       </c>
       <c r="B26" s="88" t="n">
-        <v>-0.55</v>
+        <v>-0.41</v>
       </c>
       <c r="C26" s="88" t="n">
         <v>0.25</v>
@@ -4085,7 +4085,7 @@
         </is>
       </c>
       <c r="B27" s="88" t="n">
-        <v>1.28</v>
+        <v>1.42</v>
       </c>
       <c r="C27" s="88" t="n">
         <v>2.26</v>
@@ -8409,7 +8409,7 @@
         </is>
       </c>
       <c r="B19" s="94" t="n">
-        <v>7.7</v>
+        <v>6.9</v>
       </c>
       <c r="C19" s="94" t="n">
         <v>7.7</v>
@@ -8506,7 +8506,7 @@
         </is>
       </c>
       <c r="B20" s="94" t="n">
-        <v>9.720000000000001</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="C20" s="94" t="n">
         <v>9.720000000000001</v>
@@ -8597,13 +8597,13 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="76" t="inlineStr">
+      <c r="A21" s="96" t="inlineStr">
         <is>
           <t>us500:RS2</t>
         </is>
       </c>
       <c r="B21" s="94" t="n">
-        <v>30.2</v>
+        <v>21.91</v>
       </c>
       <c r="C21" s="94" t="n">
         <v>30.2</v>
@@ -8699,9 +8699,9 @@
           <t>us30:EIDE</t>
         </is>
       </c>
-      <c r="B22" s="92" t="inlineStr">
-        <is>
-          <t>blue</t>
+      <c r="B22" s="95" t="inlineStr">
+        <is>
+          <t>green</t>
         </is>
       </c>
       <c r="C22" s="92" t="inlineStr">
@@ -8857,7 +8857,7 @@
         </is>
       </c>
       <c r="B23" s="94" t="n">
-        <v>6.61</v>
+        <v>5.82</v>
       </c>
       <c r="C23" s="94" t="n">
         <v>6.61</v>
@@ -8954,7 +8954,7 @@
         </is>
       </c>
       <c r="B24" s="94" t="n">
-        <v>6.65</v>
+        <v>5.65</v>
       </c>
       <c r="C24" s="94" t="n">
         <v>6.65</v>
@@ -9051,7 +9051,7 @@
         </is>
       </c>
       <c r="B25" s="94" t="n">
-        <v>45.44</v>
+        <v>30.26</v>
       </c>
       <c r="C25" s="94" t="n">
         <v>45.44</v>
@@ -9305,7 +9305,7 @@
         </is>
       </c>
       <c r="B27" s="94" t="n">
-        <v>9.48</v>
+        <v>8.57</v>
       </c>
       <c r="C27" s="94" t="n">
         <v>9.48</v>
@@ -9402,7 +9402,7 @@
         </is>
       </c>
       <c r="B28" s="94" t="n">
-        <v>11.3</v>
+        <v>10.11</v>
       </c>
       <c r="C28" s="94" t="n">
         <v>11.3</v>
@@ -9499,7 +9499,7 @@
         </is>
       </c>
       <c r="B29" s="94" t="n">
-        <v>37.61</v>
+        <v>29.79</v>
       </c>
       <c r="C29" s="94" t="n">
         <v>37.61</v>
@@ -9753,7 +9753,7 @@
         </is>
       </c>
       <c r="B31" s="94" t="n">
-        <v>8.449999999999999</v>
+        <v>9.25</v>
       </c>
       <c r="C31" s="94" t="n">
         <v>8.449999999999999</v>
@@ -9850,7 +9850,7 @@
         </is>
       </c>
       <c r="B32" s="94" t="n">
-        <v>-0.79</v>
+        <v>-0.87</v>
       </c>
       <c r="C32" s="94" t="n">
         <v>-0.79</v>
@@ -10649,7 +10649,7 @@
         </is>
       </c>
       <c r="B39" s="94" t="n">
-        <v>-1.37</v>
+        <v>-1.16</v>
       </c>
       <c r="C39" s="94" t="n">
         <v>1.06</v>
@@ -10746,7 +10746,7 @@
         </is>
       </c>
       <c r="B40" s="94" t="n">
-        <v>7.71</v>
+        <v>7.94</v>
       </c>
       <c r="C40" s="94" t="n">
         <v>9.050000000000001</v>
@@ -10843,7 +10843,7 @@
         </is>
       </c>
       <c r="B41" s="94" t="n">
-        <v>28.62</v>
+        <v>29.64</v>
       </c>
       <c r="C41" s="94" t="n">
         <v>36.99</v>
@@ -10939,9 +10939,9 @@
           <t>fr40:EIDE</t>
         </is>
       </c>
-      <c r="B42" s="92" t="inlineStr">
-        <is>
-          <t>blue</t>
+      <c r="B42" s="95" t="inlineStr">
+        <is>
+          <t>green</t>
         </is>
       </c>
       <c r="C42" s="92" t="inlineStr">
@@ -11097,7 +11097,7 @@
         </is>
       </c>
       <c r="B43" s="94" t="n">
-        <v>1.92</v>
+        <v>1.67</v>
       </c>
       <c r="C43" s="94" t="n">
         <v>1.92</v>
@@ -11194,7 +11194,7 @@
         </is>
       </c>
       <c r="B44" s="94" t="n">
-        <v>-9.289999999999999</v>
+        <v>-10.06</v>
       </c>
       <c r="C44" s="94" t="n">
         <v>-9.289999999999999</v>
@@ -11291,7 +11291,7 @@
         </is>
       </c>
       <c r="B45" s="94" t="n">
-        <v>37.41</v>
+        <v>31.9</v>
       </c>
       <c r="C45" s="94" t="n">
         <v>37.41</v>
@@ -11545,7 +11545,7 @@
         </is>
       </c>
       <c r="B47" s="94" t="n">
-        <v>8.640000000000001</v>
+        <v>8.02</v>
       </c>
       <c r="C47" s="94" t="n">
         <v>8.640000000000001</v>
@@ -11642,7 +11642,7 @@
         </is>
       </c>
       <c r="B48" s="94" t="n">
-        <v>2.94</v>
+        <v>2.02</v>
       </c>
       <c r="C48" s="94" t="n">
         <v>2.94</v>
@@ -11739,7 +11739,7 @@
         </is>
       </c>
       <c r="B49" s="94" t="n">
-        <v>42.99</v>
+        <v>36.56</v>
       </c>
       <c r="C49" s="94" t="n">
         <v>42.99</v>
@@ -11832,7 +11832,7 @@
     <row r="51">
       <c r="A51" s="90" t="inlineStr">
         <is>
-          <t>今日买报：ixic:RS2:37.61&lt;=38;vn:RS3:18.59&lt;=25;sensex:RS10:28.62&lt;=39</t>
+          <t>今日买报：us500:RS2:21.91&lt;=22;ixic:RS2:29.79&lt;=38;vn:RS3:18.59&lt;=25;sensex:RS10:29.64&lt;=39</t>
         </is>
       </c>
     </row>

--- a/report_2411.xlsx
+++ b/report_2411.xlsx
@@ -3888,7 +3888,7 @@
         </is>
       </c>
       <c r="B25" s="87" t="n">
-        <v>7.11</v>
+        <v>7.1</v>
       </c>
       <c r="C25" s="87" t="n">
         <v>7.11</v>
@@ -3985,7 +3985,7 @@
         </is>
       </c>
       <c r="B26" s="88" t="n">
-        <v>-0.01</v>
+        <v>-0.09</v>
       </c>
       <c r="C26" s="88" t="n">
         <v>-0.4</v>
@@ -4082,7 +4082,7 @@
         </is>
       </c>
       <c r="B27" s="88" t="n">
-        <v>0.52</v>
+        <v>0.44</v>
       </c>
       <c r="C27" s="88" t="n">
         <v>1.43</v>
@@ -8256,9 +8256,9 @@
           <t>us500:EIDE</t>
         </is>
       </c>
-      <c r="B18" s="94" t="inlineStr">
-        <is>
-          <t>green</t>
+      <c r="B18" s="91" t="inlineStr">
+        <is>
+          <t>red</t>
         </is>
       </c>
       <c r="C18" s="94" t="inlineStr">
@@ -8414,7 +8414,7 @@
         </is>
       </c>
       <c r="B19" s="93" t="n">
-        <v>6.9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="C19" s="93" t="n">
         <v>6.9</v>
@@ -8511,7 +8511,7 @@
         </is>
       </c>
       <c r="B20" s="93" t="n">
-        <v>8.880000000000001</v>
+        <v>8.94</v>
       </c>
       <c r="C20" s="93" t="n">
         <v>8.880000000000001</v>
@@ -8602,13 +8602,13 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="95" t="inlineStr">
+      <c r="A21" s="76" t="inlineStr">
         <is>
           <t>us500:RS2</t>
         </is>
       </c>
       <c r="B21" s="93" t="n">
-        <v>21.91</v>
+        <v>76.95</v>
       </c>
       <c r="C21" s="93" t="n">
         <v>21.91</v>
@@ -10206,7 +10206,7 @@
         </is>
       </c>
       <c r="B35" s="93" t="n">
-        <v>1.69</v>
+        <v>1.81</v>
       </c>
       <c r="C35" s="93" t="n">
         <v>3.01</v>
@@ -10303,7 +10303,7 @@
         </is>
       </c>
       <c r="B36" s="93" t="n">
-        <v>-2.61</v>
+        <v>-2.49</v>
       </c>
       <c r="C36" s="93" t="n">
         <v>-2.23</v>
@@ -10400,7 +10400,7 @@
         </is>
       </c>
       <c r="B37" s="93" t="n">
-        <v>18.1</v>
+        <v>23.71</v>
       </c>
       <c r="C37" s="93" t="n">
         <v>18.59</v>
@@ -10496,9 +10496,9 @@
           <t>sensex:EIDE</t>
         </is>
       </c>
-      <c r="B38" s="94" t="inlineStr">
-        <is>
-          <t>green</t>
+      <c r="B38" s="92" t="inlineStr">
+        <is>
+          <t>blue</t>
         </is>
       </c>
       <c r="C38" s="94" t="inlineStr">
@@ -10652,7 +10652,7 @@
         </is>
       </c>
       <c r="B39" s="93" t="n">
-        <v>-1.46</v>
+        <v>-0.22</v>
       </c>
       <c r="C39" s="93" t="n">
         <v>-1.16</v>
@@ -10749,7 +10749,7 @@
         </is>
       </c>
       <c r="B40" s="93" t="n">
-        <v>6.55</v>
+        <v>7.89</v>
       </c>
       <c r="C40" s="93" t="n">
         <v>7.94</v>
@@ -10840,13 +10840,13 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="95" t="inlineStr">
+      <c r="A41" s="76" t="inlineStr">
         <is>
           <t>sensex:RS10</t>
         </is>
       </c>
       <c r="B41" s="93" t="n">
-        <v>27.74</v>
+        <v>39.49</v>
       </c>
       <c r="C41" s="93" t="n">
         <v>29.64</v>
@@ -10942,9 +10942,9 @@
           <t>fr40:EIDE</t>
         </is>
       </c>
-      <c r="B42" s="94" t="inlineStr">
-        <is>
-          <t>green</t>
+      <c r="B42" s="92" t="inlineStr">
+        <is>
+          <t>blue</t>
         </is>
       </c>
       <c r="C42" s="94" t="inlineStr">
@@ -11100,7 +11100,7 @@
         </is>
       </c>
       <c r="B43" s="93" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="C43" s="93" t="n">
         <v>1.67</v>
@@ -11197,7 +11197,7 @@
         </is>
       </c>
       <c r="B44" s="93" t="n">
-        <v>-10.06</v>
+        <v>-9.02</v>
       </c>
       <c r="C44" s="93" t="n">
         <v>-10.06</v>
@@ -11294,7 +11294,7 @@
         </is>
       </c>
       <c r="B45" s="93" t="n">
-        <v>31.9</v>
+        <v>42.02</v>
       </c>
       <c r="C45" s="93" t="n">
         <v>31.9</v>
@@ -11390,9 +11390,9 @@
           <t>dax30:EIDE</t>
         </is>
       </c>
-      <c r="B46" s="94" t="inlineStr">
-        <is>
-          <t>green</t>
+      <c r="B46" s="92" t="inlineStr">
+        <is>
+          <t>blue</t>
         </is>
       </c>
       <c r="C46" s="94" t="inlineStr">
@@ -11548,7 +11548,7 @@
         </is>
       </c>
       <c r="B47" s="93" t="n">
-        <v>8.02</v>
+        <v>8.09</v>
       </c>
       <c r="C47" s="93" t="n">
         <v>8.02</v>
@@ -11645,7 +11645,7 @@
         </is>
       </c>
       <c r="B48" s="93" t="n">
-        <v>2.02</v>
+        <v>2.81</v>
       </c>
       <c r="C48" s="93" t="n">
         <v>2.02</v>
@@ -11742,7 +11742,7 @@
         </is>
       </c>
       <c r="B49" s="93" t="n">
-        <v>36.56</v>
+        <v>46.1</v>
       </c>
       <c r="C49" s="93" t="n">
         <v>36.56</v>
@@ -11835,7 +11835,7 @@
     <row r="51">
       <c r="A51" s="90" t="inlineStr">
         <is>
-          <t>今日买报：us500:RS2:21.91&lt;=22;ixic:RS2:29.79&lt;=38;vn:RS3:18.1&lt;=25;sensex:RS10:27.74&lt;=39</t>
+          <t>今日买报：ixic:RS2:29.79&lt;=38;vn:RS3:23.71&lt;=25</t>
         </is>
       </c>
     </row>

--- a/report_2411.xlsx
+++ b/report_2411.xlsx
@@ -3887,7 +3887,7 @@
         </is>
       </c>
       <c r="B25" s="87" t="n">
-        <v>7.18</v>
+        <v>7.2</v>
       </c>
       <c r="C25" s="87" t="n">
         <v>7.09</v>
@@ -3984,7 +3984,7 @@
         </is>
       </c>
       <c r="B26" s="88" t="n">
-        <v>1.31</v>
+        <v>1.54</v>
       </c>
       <c r="C26" s="88" t="n">
         <v>-0.28</v>
@@ -4081,7 +4081,7 @@
         </is>
       </c>
       <c r="B27" s="88" t="n">
-        <v>1.3</v>
+        <v>1.53</v>
       </c>
       <c r="C27" s="88" t="n">
         <v>0.25</v>
@@ -8419,7 +8419,7 @@
         </is>
       </c>
       <c r="B19" s="93" t="n">
-        <v>8.199999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="C19" s="93" t="n">
         <v>8.199999999999999</v>
@@ -8516,7 +8516,7 @@
         </is>
       </c>
       <c r="B20" s="93" t="n">
-        <v>8.94</v>
+        <v>11.93</v>
       </c>
       <c r="C20" s="93" t="n">
         <v>8.94</v>
@@ -8607,13 +8607,13 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="76" t="inlineStr">
+      <c r="A21" s="86" t="inlineStr">
         <is>
           <t>us500:RS2</t>
         </is>
       </c>
       <c r="B21" s="93" t="n">
-        <v>76.95</v>
+        <v>94.15000000000001</v>
       </c>
       <c r="C21" s="93" t="n">
         <v>76.95</v>
@@ -8709,9 +8709,9 @@
           <t>us30:EIDE</t>
         </is>
       </c>
-      <c r="B22" s="92" t="inlineStr">
-        <is>
-          <t>blue</t>
+      <c r="B22" s="91" t="inlineStr">
+        <is>
+          <t>red</t>
         </is>
       </c>
       <c r="C22" s="92" t="inlineStr">
@@ -8867,7 +8867,7 @@
         </is>
       </c>
       <c r="B23" s="93" t="n">
-        <v>7.28</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="C23" s="93" t="n">
         <v>7.28</v>
@@ -8964,7 +8964,7 @@
         </is>
       </c>
       <c r="B24" s="93" t="n">
-        <v>5.8</v>
+        <v>9.68</v>
       </c>
       <c r="C24" s="93" t="n">
         <v>5.8</v>
@@ -9055,13 +9055,13 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="76" t="inlineStr">
+      <c r="A25" s="86" t="inlineStr">
         <is>
           <t>us30:RS3</t>
         </is>
       </c>
       <c r="B25" s="93" t="n">
-        <v>61.92</v>
+        <v>88.81</v>
       </c>
       <c r="C25" s="93" t="n">
         <v>61.92</v>
@@ -9315,7 +9315,7 @@
         </is>
       </c>
       <c r="B27" s="93" t="n">
-        <v>9.880000000000001</v>
+        <v>10.45</v>
       </c>
       <c r="C27" s="93" t="n">
         <v>9.880000000000001</v>
@@ -9412,7 +9412,7 @@
         </is>
       </c>
       <c r="B28" s="93" t="n">
-        <v>10.13</v>
+        <v>13.68</v>
       </c>
       <c r="C28" s="93" t="n">
         <v>10.13</v>
@@ -9509,7 +9509,7 @@
         </is>
       </c>
       <c r="B29" s="93" t="n">
-        <v>74.91</v>
+        <v>93.22</v>
       </c>
       <c r="C29" s="93" t="n">
         <v>74.91</v>
@@ -10053,9 +10053,9 @@
           <t>vn:EIDE</t>
         </is>
       </c>
-      <c r="B34" s="92" t="inlineStr">
-        <is>
-          <t>blue</t>
+      <c r="B34" s="91" t="inlineStr">
+        <is>
+          <t>red</t>
         </is>
       </c>
       <c r="C34" s="94" t="inlineStr">
@@ -10211,7 +10211,7 @@
         </is>
       </c>
       <c r="B35" s="93" t="n">
-        <v>2.36</v>
+        <v>2.52</v>
       </c>
       <c r="C35" s="93" t="n">
         <v>1.81</v>
@@ -10308,7 +10308,7 @@
         </is>
       </c>
       <c r="B36" s="93" t="n">
-        <v>-1.39</v>
+        <v>-1.24</v>
       </c>
       <c r="C36" s="93" t="n">
         <v>-2.49</v>
@@ -10405,7 +10405,7 @@
         </is>
       </c>
       <c r="B37" s="93" t="n">
-        <v>65.63</v>
+        <v>68.13</v>
       </c>
       <c r="C37" s="93" t="n">
         <v>23.71</v>
@@ -10659,7 +10659,7 @@
         </is>
       </c>
       <c r="B39" s="93" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="C39" s="93" t="n">
         <v>-0.22</v>
@@ -10756,7 +10756,7 @@
         </is>
       </c>
       <c r="B40" s="93" t="n">
-        <v>8.720000000000001</v>
+        <v>8.74</v>
       </c>
       <c r="C40" s="93" t="n">
         <v>7.89</v>
@@ -10853,7 +10853,7 @@
         </is>
       </c>
       <c r="B41" s="93" t="n">
-        <v>49.49</v>
+        <v>49.65</v>
       </c>
       <c r="C41" s="93" t="n">
         <v>39.49</v>
@@ -11107,7 +11107,7 @@
         </is>
       </c>
       <c r="B43" s="93" t="n">
-        <v>1.69</v>
+        <v>0.49</v>
       </c>
       <c r="C43" s="93" t="n">
         <v>1.8</v>
@@ -11204,7 +11204,7 @@
         </is>
       </c>
       <c r="B44" s="93" t="n">
-        <v>-7.85</v>
+        <v>-8.93</v>
       </c>
       <c r="C44" s="93" t="n">
         <v>-9.02</v>
@@ -11301,7 +11301,7 @@
         </is>
       </c>
       <c r="B45" s="93" t="n">
-        <v>54.07</v>
+        <v>35.11</v>
       </c>
       <c r="C45" s="93" t="n">
         <v>42.02</v>
@@ -11397,9 +11397,9 @@
           <t>dax30:EIDE</t>
         </is>
       </c>
-      <c r="B46" s="91" t="inlineStr">
-        <is>
-          <t>red</t>
+      <c r="B46" s="94" t="inlineStr">
+        <is>
+          <t>green</t>
         </is>
       </c>
       <c r="C46" s="92" t="inlineStr">
@@ -11555,7 +11555,7 @@
         </is>
       </c>
       <c r="B47" s="93" t="n">
-        <v>9.289999999999999</v>
+        <v>6.45</v>
       </c>
       <c r="C47" s="93" t="n">
         <v>8.109999999999999</v>
@@ -11652,7 +11652,7 @@
         </is>
       </c>
       <c r="B48" s="93" t="n">
-        <v>4.64</v>
+        <v>1.92</v>
       </c>
       <c r="C48" s="93" t="n">
         <v>2.83</v>
@@ -11749,7 +11749,7 @@
         </is>
       </c>
       <c r="B49" s="93" t="n">
-        <v>64.08</v>
+        <v>33.82</v>
       </c>
       <c r="C49" s="93" t="n">
         <v>46.32</v>
@@ -11849,7 +11849,7 @@
     <row r="52">
       <c r="A52" s="90" t="inlineStr">
         <is>
-          <t>今日卖报：sh:RNG60:18.29&gt;=10;sh:RS3:85.82&gt;=66;kc:RNG60:41.71&gt;=25;kc:RNG120:30.1&gt;=30;kc:RS5:67.16&gt;=65;cy:RNG60:40.97&gt;=25;hk50:RNG60:21.59&gt;=15</t>
+          <t>今日卖报：sh:RNG60:18.29&gt;=10;sh:RS3:85.82&gt;=66;kc:RNG60:41.71&gt;=25;kc:RNG120:30.1&gt;=30;kc:RS5:67.16&gt;=65;cy:RNG60:40.97&gt;=25;hk50:RNG60:21.59&gt;=15;us500:RS2:94.15&gt;=85;us30:RS3:88.81&gt;=85</t>
         </is>
       </c>
     </row>

--- a/report_2411.xlsx
+++ b/report_2411.xlsx
@@ -3887,7 +3887,7 @@
         </is>
       </c>
       <c r="B25" s="87" t="n">
-        <v>7.18</v>
+        <v>7.15</v>
       </c>
       <c r="C25" s="87" t="n">
         <v>7.2</v>
@@ -3984,7 +3984,7 @@
         </is>
       </c>
       <c r="B26" s="88" t="n">
-        <v>-0.33</v>
+        <v>-0.62</v>
       </c>
       <c r="C26" s="88" t="n">
         <v>1.54</v>
@@ -4081,7 +4081,7 @@
         </is>
       </c>
       <c r="B27" s="88" t="n">
-        <v>1.31</v>
+        <v>1.01</v>
       </c>
       <c r="C27" s="88" t="n">
         <v>1.53</v>
@@ -8425,7 +8425,7 @@
         </is>
       </c>
       <c r="B19" s="93" t="n">
-        <v>9.1</v>
+        <v>9.49</v>
       </c>
       <c r="C19" s="93" t="n">
         <v>9.1</v>
@@ -8522,7 +8522,7 @@
         </is>
       </c>
       <c r="B20" s="93" t="n">
-        <v>11.93</v>
+        <v>12.63</v>
       </c>
       <c r="C20" s="93" t="n">
         <v>11.93</v>
@@ -8619,7 +8619,7 @@
         </is>
       </c>
       <c r="B21" s="93" t="n">
-        <v>94.15000000000001</v>
+        <v>95.97</v>
       </c>
       <c r="C21" s="93" t="n">
         <v>94.15000000000001</v>
@@ -10859,7 +10859,7 @@
         </is>
       </c>
       <c r="B41" s="93" t="n">
-        <v>42.34</v>
+        <v>42.32</v>
       </c>
       <c r="C41" s="93" t="n">
         <v>49.65</v>
@@ -11113,7 +11113,7 @@
         </is>
       </c>
       <c r="B43" s="93" t="n">
-        <v>0.49</v>
+        <v>0.03</v>
       </c>
       <c r="C43" s="93" t="n">
         <v>0.49</v>
@@ -11210,7 +11210,7 @@
         </is>
       </c>
       <c r="B44" s="93" t="n">
-        <v>-8.93</v>
+        <v>-8.35</v>
       </c>
       <c r="C44" s="93" t="n">
         <v>-8.93</v>
@@ -11307,7 +11307,7 @@
         </is>
       </c>
       <c r="B45" s="93" t="n">
-        <v>35.11</v>
+        <v>50.33</v>
       </c>
       <c r="C45" s="93" t="n">
         <v>35.11</v>
@@ -11403,9 +11403,9 @@
           <t>dax30:EIDE</t>
         </is>
       </c>
-      <c r="B46" s="94" t="inlineStr">
-        <is>
-          <t>green</t>
+      <c r="B46" s="91" t="inlineStr">
+        <is>
+          <t>red</t>
         </is>
       </c>
       <c r="C46" s="94" t="inlineStr">
@@ -11561,7 +11561,7 @@
         </is>
       </c>
       <c r="B47" s="93" t="n">
-        <v>6.45</v>
+        <v>6.51</v>
       </c>
       <c r="C47" s="93" t="n">
         <v>6.45</v>
@@ -11658,7 +11658,7 @@
         </is>
       </c>
       <c r="B48" s="93" t="n">
-        <v>1.92</v>
+        <v>3.62</v>
       </c>
       <c r="C48" s="93" t="n">
         <v>1.92</v>
@@ -11755,7 +11755,7 @@
         </is>
       </c>
       <c r="B49" s="93" t="n">
-        <v>33.82</v>
+        <v>55.58</v>
       </c>
       <c r="C49" s="93" t="n">
         <v>33.82</v>
@@ -11855,7 +11855,7 @@
     <row r="52">
       <c r="A52" s="90" t="inlineStr">
         <is>
-          <t>今日卖报：sh:RNG60:21.04&gt;=10;sh:RS3:94.35&gt;=66;kc:RNG60:44.07&gt;=25;kc:RNG120:34.67&gt;=30;kc:RS5:76.74&gt;=65;cy:RNG60:44.45&gt;=25;hk50:RNG60:22.6&gt;=15;us500:RS2:94.15&gt;=85;us30:RS3:88.81&gt;=85</t>
+          <t>今日卖报：sh:RNG60:21.04&gt;=10;sh:RS3:94.35&gt;=66;kc:RNG60:44.07&gt;=25;kc:RNG120:34.67&gt;=30;kc:RS5:76.74&gt;=65;cy:RNG60:44.45&gt;=25;hk50:RNG60:22.6&gt;=15;us500:RS2:95.97&gt;=85;us30:RS3:88.81&gt;=85</t>
         </is>
       </c>
     </row>

--- a/report_2411.xlsx
+++ b/report_2411.xlsx
@@ -3887,7 +3887,7 @@
         </is>
       </c>
       <c r="B25" s="87" t="n">
-        <v>7.17</v>
+        <v>7.2</v>
       </c>
       <c r="C25" s="87" t="n">
         <v>7.16</v>
@@ -3984,7 +3984,7 @@
         </is>
       </c>
       <c r="B26" s="88" t="n">
-        <v>0.23</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="C26" s="88" t="n">
         <v>-0.58</v>
@@ -4081,7 +4081,7 @@
         </is>
       </c>
       <c r="B27" s="88" t="n">
-        <v>1.52</v>
+        <v>1.84</v>
       </c>
       <c r="C27" s="88" t="n">
         <v>1.05</v>
@@ -8427,7 +8427,7 @@
         </is>
       </c>
       <c r="B19" s="93" t="n">
-        <v>9.49</v>
+        <v>8.16</v>
       </c>
       <c r="C19" s="93" t="n">
         <v>9.49</v>
@@ -8524,7 +8524,7 @@
         </is>
       </c>
       <c r="B20" s="93" t="n">
-        <v>12.63</v>
+        <v>12.95</v>
       </c>
       <c r="C20" s="93" t="n">
         <v>12.63</v>
@@ -8621,7 +8621,7 @@
         </is>
       </c>
       <c r="B21" s="93" t="n">
-        <v>95.97</v>
+        <v>96.94</v>
       </c>
       <c r="C21" s="93" t="n">
         <v>95.97</v>
@@ -8873,7 +8873,7 @@
         </is>
       </c>
       <c r="B23" s="93" t="n">
-        <v>9.300000000000001</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="C23" s="93" t="n">
         <v>9.300000000000001</v>
@@ -8970,7 +8970,7 @@
         </is>
       </c>
       <c r="B24" s="93" t="n">
-        <v>9.31</v>
+        <v>10.51</v>
       </c>
       <c r="C24" s="93" t="n">
         <v>9.31</v>
@@ -9067,7 +9067,7 @@
         </is>
       </c>
       <c r="B25" s="93" t="n">
-        <v>88.77</v>
+        <v>91.18000000000001</v>
       </c>
       <c r="C25" s="93" t="n">
         <v>88.77</v>
@@ -9319,7 +9319,7 @@
         </is>
       </c>
       <c r="B27" s="93" t="n">
-        <v>12.08</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="C27" s="93" t="n">
         <v>12.08</v>
@@ -9416,7 +9416,7 @@
         </is>
       </c>
       <c r="B28" s="93" t="n">
-        <v>15.48</v>
+        <v>14.84</v>
       </c>
       <c r="C28" s="93" t="n">
         <v>15.48</v>
@@ -9513,7 +9513,7 @@
         </is>
       </c>
       <c r="B29" s="93" t="n">
-        <v>96.16</v>
+        <v>96.34999999999999</v>
       </c>
       <c r="C29" s="93" t="n">
         <v>96.16</v>
@@ -10211,7 +10211,7 @@
         </is>
       </c>
       <c r="B35" s="93" t="n">
-        <v>1.94</v>
+        <v>1.8</v>
       </c>
       <c r="C35" s="93" t="n">
         <v>2.38</v>
@@ -10308,7 +10308,7 @@
         </is>
       </c>
       <c r="B36" s="93" t="n">
-        <v>-2.1</v>
+        <v>-2.22</v>
       </c>
       <c r="C36" s="93" t="n">
         <v>-0.57</v>
@@ -10405,7 +10405,7 @@
         </is>
       </c>
       <c r="B37" s="93" t="n">
-        <v>43.78</v>
+        <v>40.24</v>
       </c>
       <c r="C37" s="93" t="n">
         <v>62.73</v>
@@ -10754,7 +10754,7 @@
         </is>
       </c>
       <c r="B40" s="93" t="n">
-        <v>7.49</v>
+        <v>7.48</v>
       </c>
       <c r="C40" s="93" t="n">
         <v>7.48</v>
@@ -10851,7 +10851,7 @@
         </is>
       </c>
       <c r="B41" s="93" t="n">
-        <v>41.91</v>
+        <v>41.87</v>
       </c>
       <c r="C41" s="93" t="n">
         <v>42.32</v>
@@ -10947,9 +10947,9 @@
           <t>fr40:EIDE</t>
         </is>
       </c>
-      <c r="B42" s="92" t="inlineStr">
-        <is>
-          <t>blue</t>
+      <c r="B42" s="94" t="inlineStr">
+        <is>
+          <t>green</t>
         </is>
       </c>
       <c r="C42" s="92" t="inlineStr">
@@ -11103,7 +11103,7 @@
         </is>
       </c>
       <c r="B43" s="93" t="n">
-        <v>-0.16</v>
+        <v>-1.49</v>
       </c>
       <c r="C43" s="93" t="n">
         <v>0.03</v>
@@ -11200,7 +11200,7 @@
         </is>
       </c>
       <c r="B44" s="93" t="n">
-        <v>-8.119999999999999</v>
+        <v>-9.34</v>
       </c>
       <c r="C44" s="93" t="n">
         <v>-8.35</v>
@@ -11297,7 +11297,7 @@
         </is>
       </c>
       <c r="B45" s="93" t="n">
-        <v>53.36</v>
+        <v>34.59</v>
       </c>
       <c r="C45" s="93" t="n">
         <v>50.33</v>
@@ -11393,9 +11393,9 @@
           <t>dax30:EIDE</t>
         </is>
       </c>
-      <c r="B46" s="91" t="inlineStr">
-        <is>
-          <t>red</t>
+      <c r="B46" s="92" t="inlineStr">
+        <is>
+          <t>blue</t>
         </is>
       </c>
       <c r="C46" s="91" t="inlineStr">
@@ -11549,7 +11549,7 @@
         </is>
       </c>
       <c r="B47" s="93" t="n">
-        <v>6.49</v>
+        <v>4.87</v>
       </c>
       <c r="C47" s="93" t="n">
         <v>6.49</v>
@@ -11646,7 +11646,7 @@
         </is>
       </c>
       <c r="B48" s="93" t="n">
-        <v>3.59</v>
+        <v>2.79</v>
       </c>
       <c r="C48" s="93" t="n">
         <v>3.59</v>
@@ -11743,7 +11743,7 @@
         </is>
       </c>
       <c r="B49" s="93" t="n">
-        <v>55.36</v>
+        <v>47</v>
       </c>
       <c r="C49" s="93" t="n">
         <v>55.36</v>
@@ -11843,7 +11843,7 @@
     <row r="52">
       <c r="A52" s="90" t="inlineStr">
         <is>
-          <t>今日卖报：sh:RNG60:20.3&gt;=10;sh:RS3:79.24&gt;=66;kc:RNG60:44.95&gt;=25;kc:RNG120:34.9&gt;=30;kc:RS5:74.24&gt;=65;cy:RNG60:43.28&gt;=25;hk50:RNG60:21.13&gt;=15;us500:RS2:95.97&gt;=85;us30:RS3:88.77&gt;=85;ixic:RS2:96.16&gt;=96</t>
+          <t>今日卖报：sh:RNG60:20.3&gt;=10;sh:RS3:79.24&gt;=66;kc:RNG60:44.95&gt;=25;kc:RNG120:34.9&gt;=30;kc:RS5:74.24&gt;=65;cy:RNG60:43.28&gt;=25;hk50:RNG60:21.13&gt;=15;us500:RS2:96.94&gt;=85;us30:RS3:91.18&gt;=85;ixic:RS2:96.35&gt;=96</t>
         </is>
       </c>
     </row>

--- a/report_2411.xlsx
+++ b/report_2411.xlsx
@@ -3887,7 +3887,7 @@
         </is>
       </c>
       <c r="B25" s="87" t="n">
-        <v>7.21</v>
+        <v>7.23</v>
       </c>
       <c r="C25" s="87" t="n">
         <v>7.2</v>
@@ -3984,7 +3984,7 @@
         </is>
       </c>
       <c r="B26" s="88" t="n">
-        <v>0.18</v>
+        <v>0.41</v>
       </c>
       <c r="C26" s="88" t="n">
         <v>0.5600000000000001</v>
@@ -4081,7 +4081,7 @@
         </is>
       </c>
       <c r="B27" s="88" t="n">
-        <v>1.65</v>
+        <v>1.89</v>
       </c>
       <c r="C27" s="88" t="n">
         <v>1.84</v>
@@ -8443,7 +8443,7 @@
         </is>
       </c>
       <c r="B19" s="93" t="n">
-        <v>8.16</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="C19" s="93" t="n">
         <v>8.16</v>
@@ -8540,7 +8540,7 @@
         </is>
       </c>
       <c r="B20" s="93" t="n">
-        <v>12.95</v>
+        <v>12.78</v>
       </c>
       <c r="C20" s="93" t="n">
         <v>12.95</v>
@@ -8637,7 +8637,7 @@
         </is>
       </c>
       <c r="B21" s="93" t="n">
-        <v>96.94</v>
+        <v>97.27</v>
       </c>
       <c r="C21" s="93" t="n">
         <v>96.94</v>
@@ -9339,7 +9339,7 @@
         </is>
       </c>
       <c r="B27" s="93" t="n">
-        <v>9.619999999999999</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="C27" s="93" t="n">
         <v>9.619999999999999</v>
@@ -9436,7 +9436,7 @@
         </is>
       </c>
       <c r="B28" s="93" t="n">
-        <v>14.84</v>
+        <v>14.65</v>
       </c>
       <c r="C28" s="93" t="n">
         <v>14.84</v>
@@ -9533,7 +9533,7 @@
         </is>
       </c>
       <c r="B29" s="93" t="n">
-        <v>96.34999999999999</v>
+        <v>96.59</v>
       </c>
       <c r="C29" s="93" t="n">
         <v>96.34999999999999</v>
@@ -10683,7 +10683,7 @@
         </is>
       </c>
       <c r="B39" s="93" t="n">
-        <v>-1.35</v>
+        <v>-1.17</v>
       </c>
       <c r="C39" s="93" t="n">
         <v>0.5</v>
@@ -10780,7 +10780,7 @@
         </is>
       </c>
       <c r="B40" s="93" t="n">
-        <v>6.92</v>
+        <v>7.11</v>
       </c>
       <c r="C40" s="93" t="n">
         <v>7.48</v>
@@ -10877,7 +10877,7 @@
         </is>
       </c>
       <c r="B41" s="93" t="n">
-        <v>40.71</v>
+        <v>41.99</v>
       </c>
       <c r="C41" s="93" t="n">
         <v>41.87</v>
@@ -11131,7 +11131,7 @@
         </is>
       </c>
       <c r="B43" s="93" t="n">
-        <v>-1.06</v>
+        <v>-1</v>
       </c>
       <c r="C43" s="93" t="n">
         <v>-1.49</v>
@@ -11228,7 +11228,7 @@
         </is>
       </c>
       <c r="B44" s="93" t="n">
-        <v>-8.73</v>
+        <v>-8.68</v>
       </c>
       <c r="C44" s="93" t="n">
         <v>-9.34</v>
@@ -11325,7 +11325,7 @@
         </is>
       </c>
       <c r="B45" s="93" t="n">
-        <v>52.47</v>
+        <v>53.17</v>
       </c>
       <c r="C45" s="93" t="n">
         <v>34.59</v>
@@ -11421,9 +11421,9 @@
           <t>dax30:EIDE</t>
         </is>
       </c>
-      <c r="B46" s="92" t="inlineStr">
-        <is>
-          <t>blue</t>
+      <c r="B46" s="91" t="inlineStr">
+        <is>
+          <t>red</t>
         </is>
       </c>
       <c r="C46" s="92" t="inlineStr">
@@ -11579,7 +11579,7 @@
         </is>
       </c>
       <c r="B47" s="93" t="n">
-        <v>4.87</v>
+        <v>5.57</v>
       </c>
       <c r="C47" s="93" t="n">
         <v>4.87</v>
@@ -11676,7 +11676,7 @@
         </is>
       </c>
       <c r="B48" s="93" t="n">
-        <v>2.79</v>
+        <v>3.59</v>
       </c>
       <c r="C48" s="93" t="n">
         <v>2.79</v>
@@ -11773,7 +11773,7 @@
         </is>
       </c>
       <c r="B49" s="93" t="n">
-        <v>47</v>
+        <v>58.82</v>
       </c>
       <c r="C49" s="93" t="n">
         <v>47</v>
@@ -11873,7 +11873,7 @@
     <row r="52">
       <c r="A52" s="90" t="inlineStr">
         <is>
-          <t>今日卖报：sh:RNG60:20.91&gt;=10;sh:RS3:83.15&gt;=66;kc:RNG60:51.48&gt;=25;kc:RNG120:43.28&gt;=30;kc:RS5:84.85&gt;=65;cy:RNG60:48.46&gt;=25;hk50:RNG60:18.94&gt;=15;us500:RS2:96.94&gt;=85;us30:RS3:91.18&gt;=85;ixic:RS2:96.35&gt;=96</t>
+          <t>今日卖报：sh:RNG60:20.91&gt;=10;sh:RS3:83.15&gt;=66;kc:RNG60:51.48&gt;=25;kc:RNG120:43.28&gt;=30;kc:RS5:84.85&gt;=65;cy:RNG60:48.46&gt;=25;hk50:RNG60:18.94&gt;=15;us500:RS2:97.27&gt;=85;us30:RS3:91.18&gt;=85;ixic:RS2:96.59&gt;=96</t>
         </is>
       </c>
     </row>

--- a/report_2411.xlsx
+++ b/report_2411.xlsx
@@ -3985,7 +3985,7 @@
         </is>
       </c>
       <c r="B26" s="87" t="n">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="C26" s="87" t="n">
         <v>0.37</v>
@@ -4082,7 +4082,7 @@
         </is>
       </c>
       <c r="B27" s="87" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="C27" s="87" t="n">
         <v>1.84</v>
@@ -8444,7 +8444,7 @@
         </is>
       </c>
       <c r="B19" s="93" t="n">
-        <v>8.050000000000001</v>
+        <v>6.7</v>
       </c>
       <c r="C19" s="93" t="n">
         <v>8.050000000000001</v>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="B20" s="93" t="n">
-        <v>12.78</v>
+        <v>12.76</v>
       </c>
       <c r="C20" s="93" t="n">
         <v>12.78</v>
@@ -8632,13 +8632,13 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="92" t="inlineStr">
+      <c r="A21" s="76" t="inlineStr">
         <is>
           <t>us500:RS2</t>
         </is>
       </c>
       <c r="B21" s="93" t="n">
-        <v>97.27</v>
+        <v>58.57</v>
       </c>
       <c r="C21" s="93" t="n">
         <v>97.27</v>
@@ -8734,9 +8734,9 @@
           <t>us30:EIDE</t>
         </is>
       </c>
-      <c r="B22" s="91" t="inlineStr">
-        <is>
-          <t>red</t>
+      <c r="B22" s="90" t="inlineStr">
+        <is>
+          <t>blue</t>
         </is>
       </c>
       <c r="C22" s="91" t="inlineStr">
@@ -8892,7 +8892,7 @@
         </is>
       </c>
       <c r="B23" s="93" t="n">
-        <v>8.94</v>
+        <v>7.37</v>
       </c>
       <c r="C23" s="93" t="n">
         <v>8.94</v>
@@ -8989,7 +8989,7 @@
         </is>
       </c>
       <c r="B24" s="93" t="n">
-        <v>11.09</v>
+        <v>10.69</v>
       </c>
       <c r="C24" s="93" t="n">
         <v>11.09</v>
@@ -9080,13 +9080,13 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="92" t="inlineStr">
+      <c r="A25" s="76" t="inlineStr">
         <is>
           <t>us30:RS3</t>
         </is>
       </c>
       <c r="B25" s="93" t="n">
-        <v>93.59999999999999</v>
+        <v>61.73</v>
       </c>
       <c r="C25" s="93" t="n">
         <v>93.59999999999999</v>
@@ -9340,7 +9340,7 @@
         </is>
       </c>
       <c r="B27" s="93" t="n">
-        <v>9.449999999999999</v>
+        <v>7.86</v>
       </c>
       <c r="C27" s="93" t="n">
         <v>9.449999999999999</v>
@@ -9437,7 +9437,7 @@
         </is>
       </c>
       <c r="B28" s="93" t="n">
-        <v>14.65</v>
+        <v>14.76</v>
       </c>
       <c r="C28" s="93" t="n">
         <v>14.65</v>
@@ -9528,13 +9528,13 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="92" t="inlineStr">
+      <c r="A29" s="76" t="inlineStr">
         <is>
           <t>ixic:RS2</t>
         </is>
       </c>
       <c r="B29" s="93" t="n">
-        <v>96.59</v>
+        <v>81.34999999999999</v>
       </c>
       <c r="C29" s="93" t="n">
         <v>96.59</v>
@@ -9630,9 +9630,9 @@
           <t>jp225:EIDE</t>
         </is>
       </c>
-      <c r="B30" s="91" t="inlineStr">
-        <is>
-          <t>red</t>
+      <c r="B30" s="90" t="inlineStr">
+        <is>
+          <t>blue</t>
         </is>
       </c>
       <c r="C30" s="91" t="inlineStr">
@@ -9788,7 +9788,7 @@
         </is>
       </c>
       <c r="B31" s="93" t="n">
-        <v>4.31</v>
+        <v>3.45</v>
       </c>
       <c r="C31" s="93" t="n">
         <v>7.64</v>
@@ -9885,7 +9885,7 @@
         </is>
       </c>
       <c r="B32" s="93" t="n">
-        <v>1.54</v>
+        <v>0.7</v>
       </c>
       <c r="C32" s="93" t="n">
         <v>2.37</v>
@@ -9982,7 +9982,7 @@
         </is>
       </c>
       <c r="B33" s="93" t="n">
-        <v>63.67</v>
+        <v>58.04</v>
       </c>
       <c r="C33" s="93" t="n">
         <v>61.38</v>
@@ -11132,7 +11132,7 @@
         </is>
       </c>
       <c r="B43" s="93" t="n">
-        <v>-2</v>
+        <v>-3.46</v>
       </c>
       <c r="C43" s="93" t="n">
         <v>-1</v>
@@ -11229,7 +11229,7 @@
         </is>
       </c>
       <c r="B44" s="93" t="n">
-        <v>-8.960000000000001</v>
+        <v>-10.31</v>
       </c>
       <c r="C44" s="93" t="n">
         <v>-8.68</v>
@@ -11326,7 +11326,7 @@
         </is>
       </c>
       <c r="B45" s="93" t="n">
-        <v>38.9</v>
+        <v>29.46</v>
       </c>
       <c r="C45" s="93" t="n">
         <v>53.17</v>
@@ -11422,9 +11422,9 @@
           <t>dax30:EIDE</t>
         </is>
       </c>
-      <c r="B46" s="90" t="inlineStr">
-        <is>
-          <t>blue</t>
+      <c r="B46" s="94" t="inlineStr">
+        <is>
+          <t>green</t>
         </is>
       </c>
       <c r="C46" s="91" t="inlineStr">
@@ -11580,7 +11580,7 @@
         </is>
       </c>
       <c r="B47" s="93" t="n">
-        <v>4.98</v>
+        <v>3.68</v>
       </c>
       <c r="C47" s="93" t="n">
         <v>5.57</v>
@@ -11677,7 +11677,7 @@
         </is>
       </c>
       <c r="B48" s="93" t="n">
-        <v>3.18</v>
+        <v>1.9</v>
       </c>
       <c r="C48" s="93" t="n">
         <v>3.59</v>
@@ -11774,7 +11774,7 @@
         </is>
       </c>
       <c r="B49" s="93" t="n">
-        <v>48.9</v>
+        <v>39.84</v>
       </c>
       <c r="C49" s="93" t="n">
         <v>58.82</v>
@@ -11874,7 +11874,7 @@
     <row r="52">
       <c r="A52" s="89" t="inlineStr">
         <is>
-          <t>今日卖报：sh:RNG60:19.56&gt;=10;kc:RNG60:48.9&gt;=25;kc:RNG120:40.73&gt;=30;kc:RS5:67.94&gt;=65;cy:RNG60:49.83&gt;=25;hk50:RNG60:15.97&gt;=15;us500:RS2:97.27&gt;=85;us30:RS3:93.6&gt;=85;ixic:RS2:96.59&gt;=96</t>
+          <t>今日卖报：sh:RNG60:19.56&gt;=10;kc:RNG60:48.9&gt;=25;kc:RNG120:40.73&gt;=30;kc:RS5:67.94&gt;=65;cy:RNG60:49.83&gt;=25;hk50:RNG60:15.97&gt;=15</t>
         </is>
       </c>
     </row>

--- a/report_2411.xlsx
+++ b/report_2411.xlsx
@@ -3888,7 +3888,7 @@
         </is>
       </c>
       <c r="B25" s="86" t="n">
-        <v>7.22</v>
+        <v>7.24</v>
       </c>
       <c r="C25" s="86" t="n">
         <v>7.24</v>
@@ -3985,7 +3985,7 @@
         </is>
       </c>
       <c r="B26" s="87" t="n">
-        <v>-0.28</v>
+        <v>-0.02</v>
       </c>
       <c r="C26" s="87" t="n">
         <v>0.27</v>
@@ -4082,7 +4082,7 @@
         </is>
       </c>
       <c r="B27" s="87" t="n">
-        <v>1.24</v>
+        <v>1.52</v>
       </c>
       <c r="C27" s="87" t="n">
         <v>1.46</v>
@@ -8286,9 +8286,9 @@
           <t>us500:EIDE</t>
         </is>
       </c>
-      <c r="B18" s="91" t="inlineStr">
-        <is>
-          <t>red</t>
+      <c r="B18" s="90" t="inlineStr">
+        <is>
+          <t>blue</t>
         </is>
       </c>
       <c r="C18" s="91" t="inlineStr">
@@ -8444,7 +8444,7 @@
         </is>
       </c>
       <c r="B19" s="93" t="n">
-        <v>6.7</v>
+        <v>6.94</v>
       </c>
       <c r="C19" s="93" t="n">
         <v>6.7</v>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="B20" s="93" t="n">
-        <v>12.76</v>
+        <v>13.62</v>
       </c>
       <c r="C20" s="93" t="n">
         <v>12.76</v>
@@ -8638,7 +8638,7 @@
         </is>
       </c>
       <c r="B21" s="93" t="n">
-        <v>58.57</v>
+        <v>61.05</v>
       </c>
       <c r="C21" s="93" t="n">
         <v>58.57</v>
@@ -8892,7 +8892,7 @@
         </is>
       </c>
       <c r="B23" s="93" t="n">
-        <v>7.37</v>
+        <v>7.65</v>
       </c>
       <c r="C23" s="93" t="n">
         <v>7.37</v>
@@ -8989,7 +8989,7 @@
         </is>
       </c>
       <c r="B24" s="93" t="n">
-        <v>10.69</v>
+        <v>12.53</v>
       </c>
       <c r="C24" s="93" t="n">
         <v>10.69</v>
@@ -9086,7 +9086,7 @@
         </is>
       </c>
       <c r="B25" s="93" t="n">
-        <v>61.73</v>
+        <v>64</v>
       </c>
       <c r="C25" s="93" t="n">
         <v>61.73</v>
@@ -9182,9 +9182,9 @@
           <t>ixic:EIDE</t>
         </is>
       </c>
-      <c r="B26" s="91" t="inlineStr">
-        <is>
-          <t>red</t>
+      <c r="B26" s="90" t="inlineStr">
+        <is>
+          <t>blue</t>
         </is>
       </c>
       <c r="C26" s="91" t="inlineStr">
@@ -9340,7 +9340,7 @@
         </is>
       </c>
       <c r="B27" s="93" t="n">
-        <v>7.86</v>
+        <v>7.94</v>
       </c>
       <c r="C27" s="93" t="n">
         <v>7.86</v>
@@ -9437,7 +9437,7 @@
         </is>
       </c>
       <c r="B28" s="93" t="n">
-        <v>14.76</v>
+        <v>14.91</v>
       </c>
       <c r="C28" s="93" t="n">
         <v>14.76</v>
@@ -9534,7 +9534,7 @@
         </is>
       </c>
       <c r="B29" s="93" t="n">
-        <v>81.34999999999999</v>
+        <v>42.36</v>
       </c>
       <c r="C29" s="93" t="n">
         <v>81.34999999999999</v>
@@ -10684,7 +10684,7 @@
         </is>
       </c>
       <c r="B39" s="93" t="n">
-        <v>-3.95</v>
+        <v>-3.85</v>
       </c>
       <c r="C39" s="93" t="n">
         <v>-2.18</v>
@@ -10781,7 +10781,7 @@
         </is>
       </c>
       <c r="B40" s="93" t="n">
-        <v>2.92</v>
+        <v>3.02</v>
       </c>
       <c r="C40" s="93" t="n">
         <v>4.32</v>
@@ -10878,7 +10878,7 @@
         </is>
       </c>
       <c r="B41" s="93" t="n">
-        <v>28.42</v>
+        <v>28.81</v>
       </c>
       <c r="C41" s="93" t="n">
         <v>35.11</v>
@@ -11132,7 +11132,7 @@
         </is>
       </c>
       <c r="B43" s="93" t="n">
-        <v>-3.69</v>
+        <v>-4.09</v>
       </c>
       <c r="C43" s="93" t="n">
         <v>-3.46</v>
@@ -11229,7 +11229,7 @@
         </is>
       </c>
       <c r="B44" s="93" t="n">
-        <v>-8.67</v>
+        <v>-9.050000000000001</v>
       </c>
       <c r="C44" s="93" t="n">
         <v>-10.31</v>
@@ -11326,7 +11326,7 @@
         </is>
       </c>
       <c r="B45" s="93" t="n">
-        <v>33.25</v>
+        <v>28.65</v>
       </c>
       <c r="C45" s="93" t="n">
         <v>29.46</v>
@@ -11580,7 +11580,7 @@
         </is>
       </c>
       <c r="B47" s="93" t="n">
-        <v>3.19</v>
+        <v>3</v>
       </c>
       <c r="C47" s="93" t="n">
         <v>3.68</v>
@@ -11677,7 +11677,7 @@
         </is>
       </c>
       <c r="B48" s="93" t="n">
-        <v>3.05</v>
+        <v>2.87</v>
       </c>
       <c r="C48" s="93" t="n">
         <v>1.9</v>
@@ -11774,7 +11774,7 @@
         </is>
       </c>
       <c r="B49" s="93" t="n">
-        <v>40.02</v>
+        <v>38.74</v>
       </c>
       <c r="C49" s="93" t="n">
         <v>39.84</v>
@@ -11867,7 +11867,7 @@
     <row r="51">
       <c r="A51" s="89" t="inlineStr">
         <is>
-          <t>今日买报：sensex:RS10:28.42&lt;=39</t>
+          <t>今日买报：sensex:RS10:28.81&lt;=39</t>
         </is>
       </c>
     </row>

--- a/report_2411.xlsx
+++ b/report_2411.xlsx
@@ -3888,7 +3888,7 @@
         </is>
       </c>
       <c r="B25" s="86" t="n">
-        <v>7.24</v>
+        <v>7.25</v>
       </c>
       <c r="C25" s="86" t="n">
         <v>7.24</v>
@@ -3985,7 +3985,7 @@
         </is>
       </c>
       <c r="B26" s="87" t="n">
-        <v>-0.01</v>
+        <v>0.04</v>
       </c>
       <c r="C26" s="87" t="n">
         <v>-0.01</v>
@@ -4082,7 +4082,7 @@
         </is>
       </c>
       <c r="B27" s="87" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="C27" s="87" t="n">
         <v>1.52</v>
@@ -8440,7 +8440,7 @@
         </is>
       </c>
       <c r="B19" s="93" t="n">
-        <v>6.94</v>
+        <v>5.84</v>
       </c>
       <c r="C19" s="93" t="n">
         <v>6.94</v>
@@ -8537,7 +8537,7 @@
         </is>
       </c>
       <c r="B20" s="93" t="n">
-        <v>13.62</v>
+        <v>12.15</v>
       </c>
       <c r="C20" s="93" t="n">
         <v>13.62</v>
@@ -8628,13 +8628,13 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="76" t="inlineStr">
+      <c r="A21" s="95" t="inlineStr">
         <is>
           <t>us500:RS2</t>
         </is>
       </c>
       <c r="B21" s="93" t="n">
-        <v>61.05</v>
+        <v>14.82</v>
       </c>
       <c r="C21" s="93" t="n">
         <v>61.05</v>
@@ -8888,7 +8888,7 @@
         </is>
       </c>
       <c r="B23" s="93" t="n">
-        <v>7.65</v>
+        <v>7</v>
       </c>
       <c r="C23" s="93" t="n">
         <v>7.65</v>
@@ -8985,7 +8985,7 @@
         </is>
       </c>
       <c r="B24" s="93" t="n">
-        <v>12.53</v>
+        <v>11.98</v>
       </c>
       <c r="C24" s="93" t="n">
         <v>12.53</v>
@@ -9082,7 +9082,7 @@
         </is>
       </c>
       <c r="B25" s="93" t="n">
-        <v>64</v>
+        <v>46.01</v>
       </c>
       <c r="C25" s="93" t="n">
         <v>64</v>
@@ -9336,7 +9336,7 @@
         </is>
       </c>
       <c r="B27" s="93" t="n">
-        <v>7.94</v>
+        <v>6.63</v>
       </c>
       <c r="C27" s="93" t="n">
         <v>7.94</v>
@@ -9433,7 +9433,7 @@
         </is>
       </c>
       <c r="B28" s="93" t="n">
-        <v>14.91</v>
+        <v>12.92</v>
       </c>
       <c r="C28" s="93" t="n">
         <v>14.91</v>
@@ -9524,13 +9524,13 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="76" t="inlineStr">
+      <c r="A29" s="95" t="inlineStr">
         <is>
           <t>ixic:RS2</t>
         </is>
       </c>
       <c r="B29" s="93" t="n">
-        <v>42.36</v>
+        <v>12.72</v>
       </c>
       <c r="C29" s="93" t="n">
         <v>42.36</v>
@@ -11128,7 +11128,7 @@
         </is>
       </c>
       <c r="B43" s="93" t="n">
-        <v>-3.05</v>
+        <v>-2.82</v>
       </c>
       <c r="C43" s="93" t="n">
         <v>-4.09</v>
@@ -11225,7 +11225,7 @@
         </is>
       </c>
       <c r="B44" s="93" t="n">
-        <v>-8.57</v>
+        <v>-8.359999999999999</v>
       </c>
       <c r="C44" s="93" t="n">
         <v>-9.050000000000001</v>
@@ -11322,7 +11322,7 @@
         </is>
       </c>
       <c r="B45" s="93" t="n">
-        <v>43.53</v>
+        <v>46.02</v>
       </c>
       <c r="C45" s="93" t="n">
         <v>28.65</v>
@@ -11418,9 +11418,9 @@
           <t>dax30:EIDE</t>
         </is>
       </c>
-      <c r="B46" s="90" t="inlineStr">
-        <is>
-          <t>blue</t>
+      <c r="B46" s="91" t="inlineStr">
+        <is>
+          <t>red</t>
         </is>
       </c>
       <c r="C46" s="94" t="inlineStr">
@@ -11576,7 +11576,7 @@
         </is>
       </c>
       <c r="B47" s="93" t="n">
-        <v>3.93</v>
+        <v>4.17</v>
       </c>
       <c r="C47" s="93" t="n">
         <v>3</v>
@@ -11673,7 +11673,7 @@
         </is>
       </c>
       <c r="B48" s="93" t="n">
-        <v>3.91</v>
+        <v>4.15</v>
       </c>
       <c r="C48" s="93" t="n">
         <v>2.87</v>
@@ -11770,7 +11770,7 @@
         </is>
       </c>
       <c r="B49" s="93" t="n">
-        <v>50.47</v>
+        <v>52.28</v>
       </c>
       <c r="C49" s="93" t="n">
         <v>38.74</v>
@@ -11863,7 +11863,7 @@
     <row r="51">
       <c r="A51" s="89" t="inlineStr">
         <is>
-          <t>今日买报：hk50:RS4:15.45&lt;=22;vn:RS3:10.93&lt;=25;sensex:RS10:28.18&lt;=39</t>
+          <t>今日买报：hk50:RS4:15.45&lt;=22;us500:RS2:14.82&lt;=22;ixic:RS2:12.72&lt;=38;vn:RS3:10.93&lt;=25;sensex:RS10:28.18&lt;=39</t>
         </is>
       </c>
     </row>

--- a/report_2411.xlsx
+++ b/report_2411.xlsx
@@ -3891,7 +3891,7 @@
         </is>
       </c>
       <c r="B25" s="87" t="n">
-        <v>7.23</v>
+        <v>7.24</v>
       </c>
       <c r="C25" s="87" t="n">
         <v>7.25</v>
@@ -3988,7 +3988,7 @@
         </is>
       </c>
       <c r="B26" s="88" t="n">
-        <v>-0.26</v>
+        <v>-0.21</v>
       </c>
       <c r="C26" s="88" t="n">
         <v>0.13</v>
@@ -4085,7 +4085,7 @@
         </is>
       </c>
       <c r="B27" s="88" t="n">
-        <v>1.64</v>
+        <v>1.69</v>
       </c>
       <c r="C27" s="88" t="n">
         <v>1.6</v>
@@ -4570,10 +4570,10 @@
         </is>
       </c>
       <c r="B32" s="85" t="n">
-        <v>-32070</v>
+        <v>0</v>
       </c>
       <c r="C32" s="85" t="n">
-        <v>-44275</v>
+        <v>0</v>
       </c>
       <c r="D32" s="85" t="n">
         <v>-44957</v>
@@ -4670,7 +4670,7 @@
         <v>0</v>
       </c>
       <c r="C33" s="85" t="n">
-        <v>5378</v>
+        <v>0</v>
       </c>
       <c r="D33" s="85" t="n">
         <v>6400</v>
@@ -4764,10 +4764,10 @@
         </is>
       </c>
       <c r="B34" s="85" t="n">
-        <v>-29516</v>
+        <v>0</v>
       </c>
       <c r="C34" s="85" t="n">
-        <v>-30219</v>
+        <v>0</v>
       </c>
       <c r="D34" s="85" t="n">
         <v>-29015</v>
@@ -4864,7 +4864,7 @@
         <v>0</v>
       </c>
       <c r="C35" s="85" t="n">
-        <v>1870</v>
+        <v>0</v>
       </c>
       <c r="D35" s="85" t="n">
         <v>3198</v>
@@ -4961,7 +4961,7 @@
         <v>0</v>
       </c>
       <c r="C36" s="85" t="n">
-        <v>8831</v>
+        <v>0</v>
       </c>
       <c r="D36" s="85" t="n">
         <v>11499</v>
@@ -5055,10 +5055,10 @@
         </is>
       </c>
       <c r="B37" s="85" t="n">
-        <v>171143</v>
+        <v>0</v>
       </c>
       <c r="C37" s="85" t="n">
-        <v>159067</v>
+        <v>0</v>
       </c>
       <c r="D37" s="85" t="n">
         <v>171804</v>
@@ -5152,10 +5152,10 @@
         </is>
       </c>
       <c r="B38" s="85" t="n">
-        <v>68414</v>
+        <v>0</v>
       </c>
       <c r="C38" s="85" t="n">
-        <v>64752</v>
+        <v>0</v>
       </c>
       <c r="D38" s="85" t="n">
         <v>68008</v>
@@ -5252,7 +5252,7 @@
         <v>0</v>
       </c>
       <c r="C39" s="85" t="n">
-        <v>3562</v>
+        <v>0</v>
       </c>
       <c r="D39" s="85" t="n">
         <v>3303</v>
@@ -8281,9 +8281,9 @@
           <t>us500:EIDE</t>
         </is>
       </c>
-      <c r="B18" s="92" t="inlineStr">
-        <is>
-          <t>blue</t>
+      <c r="B18" s="91" t="inlineStr">
+        <is>
+          <t>green</t>
         </is>
       </c>
       <c r="C18" s="92" t="inlineStr">
@@ -8437,7 +8437,7 @@
         </is>
       </c>
       <c r="B19" s="95" t="n">
-        <v>5.84</v>
+        <v>5.39</v>
       </c>
       <c r="C19" s="95" t="n">
         <v>5.84</v>
@@ -8534,7 +8534,7 @@
         </is>
       </c>
       <c r="B20" s="95" t="n">
-        <v>12.15</v>
+        <v>10.64</v>
       </c>
       <c r="C20" s="95" t="n">
         <v>12.15</v>
@@ -8631,7 +8631,7 @@
         </is>
       </c>
       <c r="B21" s="95" t="n">
-        <v>14.82</v>
+        <v>3.46</v>
       </c>
       <c r="C21" s="95" t="n">
         <v>14.82</v>
@@ -8883,7 +8883,7 @@
         </is>
       </c>
       <c r="B23" s="95" t="n">
-        <v>7</v>
+        <v>6.71</v>
       </c>
       <c r="C23" s="95" t="n">
         <v>7</v>
@@ -8980,7 +8980,7 @@
         </is>
       </c>
       <c r="B24" s="95" t="n">
-        <v>11.98</v>
+        <v>11.82</v>
       </c>
       <c r="C24" s="95" t="n">
         <v>11.98</v>
@@ -9077,7 +9077,7 @@
         </is>
       </c>
       <c r="B25" s="95" t="n">
-        <v>46.01</v>
+        <v>28.37</v>
       </c>
       <c r="C25" s="95" t="n">
         <v>46.01</v>
@@ -9173,9 +9173,9 @@
           <t>ixic:EIDE</t>
         </is>
       </c>
-      <c r="B26" s="92" t="inlineStr">
-        <is>
-          <t>blue</t>
+      <c r="B26" s="91" t="inlineStr">
+        <is>
+          <t>green</t>
         </is>
       </c>
       <c r="C26" s="92" t="inlineStr">
@@ -9329,7 +9329,7 @@
         </is>
       </c>
       <c r="B27" s="95" t="n">
-        <v>6.63</v>
+        <v>6.02</v>
       </c>
       <c r="C27" s="95" t="n">
         <v>6.63</v>
@@ -9426,7 +9426,7 @@
         </is>
       </c>
       <c r="B28" s="95" t="n">
-        <v>12.92</v>
+        <v>9.75</v>
       </c>
       <c r="C28" s="95" t="n">
         <v>12.92</v>
@@ -9523,7 +9523,7 @@
         </is>
       </c>
       <c r="B29" s="95" t="n">
-        <v>12.72</v>
+        <v>2.17</v>
       </c>
       <c r="C29" s="95" t="n">
         <v>12.72</v>
@@ -11111,7 +11111,7 @@
         </is>
       </c>
       <c r="B43" s="95" t="n">
-        <v>-3.67</v>
+        <v>-4.06</v>
       </c>
       <c r="C43" s="95" t="n">
         <v>-2.82</v>
@@ -11208,7 +11208,7 @@
         </is>
       </c>
       <c r="B44" s="95" t="n">
-        <v>-8.69</v>
+        <v>-9.050000000000001</v>
       </c>
       <c r="C44" s="95" t="n">
         <v>-8.359999999999999</v>
@@ -11305,7 +11305,7 @@
         </is>
       </c>
       <c r="B45" s="95" t="n">
-        <v>44.16</v>
+        <v>40.54</v>
       </c>
       <c r="C45" s="95" t="n">
         <v>46.02</v>
@@ -11401,9 +11401,9 @@
           <t>dax30:EIDE</t>
         </is>
       </c>
-      <c r="B46" s="93" t="inlineStr">
-        <is>
-          <t>red</t>
+      <c r="B46" s="92" t="inlineStr">
+        <is>
+          <t>blue</t>
         </is>
       </c>
       <c r="C46" s="93" t="inlineStr">
@@ -11557,7 +11557,7 @@
         </is>
       </c>
       <c r="B47" s="95" t="n">
-        <v>3.38</v>
+        <v>3.1</v>
       </c>
       <c r="C47" s="95" t="n">
         <v>4.17</v>
@@ -11654,7 +11654,7 @@
         </is>
       </c>
       <c r="B48" s="95" t="n">
-        <v>4.13</v>
+        <v>3.85</v>
       </c>
       <c r="C48" s="95" t="n">
         <v>4.15</v>
@@ -11751,7 +11751,7 @@
         </is>
       </c>
       <c r="B49" s="95" t="n">
-        <v>52.22</v>
+        <v>49.61</v>
       </c>
       <c r="C49" s="95" t="n">
         <v>52.28</v>
@@ -11844,7 +11844,7 @@
     <row r="51">
       <c r="A51" s="90" t="inlineStr">
         <is>
-          <t>今日买报：hk50:RS4:15.29&lt;=22;us500:RS2:14.82&lt;=22;ixic:RS2:12.72&lt;=38;vn:RS3:5.73&lt;=25;sensex:RS10:28.18&lt;=39</t>
+          <t>今日买报：hk50:RS4:15.29&lt;=22;us500:RS2:3.46&lt;=22;ixic:RS2:2.17&lt;=38;vn:RS3:5.73&lt;=25;sensex:RS10:28.18&lt;=39</t>
         </is>
       </c>
     </row>

--- a/report_2411.xlsx
+++ b/report_2411.xlsx
@@ -3891,7 +3891,7 @@
         </is>
       </c>
       <c r="B25" s="87" t="n">
-        <v>7.24</v>
+        <v>7.23</v>
       </c>
       <c r="C25" s="87" t="n">
         <v>7.24</v>
@@ -3988,7 +3988,7 @@
         </is>
       </c>
       <c r="B26" s="88" t="n">
-        <v>0.12</v>
+        <v>-0.14</v>
       </c>
       <c r="C26" s="88" t="n">
         <v>-0.21</v>
@@ -4085,7 +4085,7 @@
         </is>
       </c>
       <c r="B27" s="88" t="n">
-        <v>1.5</v>
+        <v>1.24</v>
       </c>
       <c r="C27" s="88" t="n">
         <v>1.69</v>
@@ -8447,7 +8447,7 @@
         </is>
       </c>
       <c r="B19" s="95" t="n">
-        <v>5.39</v>
+        <v>4.6</v>
       </c>
       <c r="C19" s="95" t="n">
         <v>5.39</v>
@@ -8544,7 +8544,7 @@
         </is>
       </c>
       <c r="B20" s="95" t="n">
-        <v>10.64</v>
+        <v>11.9</v>
       </c>
       <c r="C20" s="95" t="n">
         <v>10.64</v>
@@ -8635,13 +8635,13 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="96" t="inlineStr">
+      <c r="A21" s="76" t="inlineStr">
         <is>
           <t>us500:RS2</t>
         </is>
       </c>
       <c r="B21" s="95" t="n">
-        <v>3.46</v>
+        <v>33.37</v>
       </c>
       <c r="C21" s="95" t="n">
         <v>3.46</v>
@@ -9343,7 +9343,7 @@
         </is>
       </c>
       <c r="B27" s="95" t="n">
-        <v>6.02</v>
+        <v>5.11</v>
       </c>
       <c r="C27" s="95" t="n">
         <v>6.02</v>
@@ -9440,7 +9440,7 @@
         </is>
       </c>
       <c r="B28" s="95" t="n">
-        <v>9.75</v>
+        <v>11.06</v>
       </c>
       <c r="C28" s="95" t="n">
         <v>9.75</v>
@@ -9537,7 +9537,7 @@
         </is>
       </c>
       <c r="B29" s="95" t="n">
-        <v>2.17</v>
+        <v>31.75</v>
       </c>
       <c r="C29" s="95" t="n">
         <v>2.17</v>
@@ -11135,7 +11135,7 @@
         </is>
       </c>
       <c r="B43" s="95" t="n">
-        <v>-4.37</v>
+        <v>-4.11</v>
       </c>
       <c r="C43" s="95" t="n">
         <v>-4.06</v>
@@ -11232,7 +11232,7 @@
         </is>
       </c>
       <c r="B44" s="95" t="n">
-        <v>-9.25</v>
+        <v>-9</v>
       </c>
       <c r="C44" s="95" t="n">
         <v>-9.050000000000001</v>
@@ -11329,7 +11329,7 @@
         </is>
       </c>
       <c r="B45" s="95" t="n">
-        <v>39.02</v>
+        <v>42.3</v>
       </c>
       <c r="C45" s="95" t="n">
         <v>40.54</v>
@@ -11583,7 +11583,7 @@
         </is>
       </c>
       <c r="B47" s="95" t="n">
-        <v>3.19</v>
+        <v>3.07</v>
       </c>
       <c r="C47" s="95" t="n">
         <v>3.1</v>
@@ -11680,7 +11680,7 @@
         </is>
       </c>
       <c r="B48" s="95" t="n">
-        <v>3.24</v>
+        <v>3.12</v>
       </c>
       <c r="C48" s="95" t="n">
         <v>3.85</v>
@@ -11777,7 +11777,7 @@
         </is>
       </c>
       <c r="B49" s="95" t="n">
-        <v>49.65</v>
+        <v>48.4</v>
       </c>
       <c r="C49" s="95" t="n">
         <v>49.61</v>
@@ -11870,7 +11870,7 @@
     <row r="51">
       <c r="A51" s="90" t="inlineStr">
         <is>
-          <t>今日买报：us500:RS2:3.46&lt;=22;ixic:RS2:2.17&lt;=38;vn:RS3:5.32&lt;=25;sensex:RS10:26.76&lt;=39</t>
+          <t>今日买报：ixic:RS2:31.75&lt;=38;vn:RS3:5.32&lt;=25;sensex:RS10:26.76&lt;=39</t>
         </is>
       </c>
     </row>

--- a/report_2411.xlsx
+++ b/report_2411.xlsx
@@ -3891,7 +3891,7 @@
         </is>
       </c>
       <c r="B25" s="87" t="n">
-        <v>7.24</v>
+        <v>7.23</v>
       </c>
       <c r="C25" s="87" t="n">
         <v>7.23</v>
@@ -3988,7 +3988,7 @@
         </is>
       </c>
       <c r="B26" s="88" t="n">
-        <v>0.14</v>
+        <v>0.08</v>
       </c>
       <c r="C26" s="88" t="n">
         <v>-0.13</v>
@@ -4085,7 +4085,7 @@
         </is>
       </c>
       <c r="B27" s="88" t="n">
-        <v>1.41</v>
+        <v>1.35</v>
       </c>
       <c r="C27" s="88" t="n">
         <v>1.25</v>
@@ -8289,9 +8289,9 @@
           <t>us500:EIDE</t>
         </is>
       </c>
-      <c r="B18" s="91" t="inlineStr">
-        <is>
-          <t>green</t>
+      <c r="B18" s="92" t="inlineStr">
+        <is>
+          <t>blue</t>
         </is>
       </c>
       <c r="C18" s="91" t="inlineStr">
@@ -8447,7 +8447,7 @@
         </is>
       </c>
       <c r="B19" s="95" t="n">
-        <v>4.6</v>
+        <v>5.34</v>
       </c>
       <c r="C19" s="95" t="n">
         <v>4.6</v>
@@ -8544,7 +8544,7 @@
         </is>
       </c>
       <c r="B20" s="95" t="n">
-        <v>11.9</v>
+        <v>13.02</v>
       </c>
       <c r="C20" s="95" t="n">
         <v>11.9</v>
@@ -8641,7 +8641,7 @@
         </is>
       </c>
       <c r="B21" s="95" t="n">
-        <v>33.37</v>
+        <v>59.11</v>
       </c>
       <c r="C21" s="95" t="n">
         <v>33.37</v>
@@ -8737,9 +8737,9 @@
           <t>us30:EIDE</t>
         </is>
       </c>
-      <c r="B22" s="92" t="inlineStr">
-        <is>
-          <t>blue</t>
+      <c r="B22" s="91" t="inlineStr">
+        <is>
+          <t>green</t>
         </is>
       </c>
       <c r="C22" s="92" t="inlineStr">
@@ -8895,7 +8895,7 @@
         </is>
       </c>
       <c r="B23" s="95" t="n">
-        <v>5.38</v>
+        <v>4.92</v>
       </c>
       <c r="C23" s="95" t="n">
         <v>5.38</v>
@@ -8992,7 +8992,7 @@
         </is>
       </c>
       <c r="B24" s="95" t="n">
-        <v>12.87</v>
+        <v>13.53</v>
       </c>
       <c r="C24" s="95" t="n">
         <v>12.87</v>
@@ -9083,13 +9083,13 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="76" t="inlineStr">
+      <c r="A25" s="96" t="inlineStr">
         <is>
           <t>us30:RS3</t>
         </is>
       </c>
       <c r="B25" s="95" t="n">
-        <v>25.69</v>
+        <v>19.64</v>
       </c>
       <c r="C25" s="95" t="n">
         <v>25.69</v>
@@ -9185,9 +9185,9 @@
           <t>ixic:EIDE</t>
         </is>
       </c>
-      <c r="B26" s="91" t="inlineStr">
-        <is>
-          <t>green</t>
+      <c r="B26" s="92" t="inlineStr">
+        <is>
+          <t>blue</t>
         </is>
       </c>
       <c r="C26" s="91" t="inlineStr">
@@ -9343,7 +9343,7 @@
         </is>
       </c>
       <c r="B27" s="95" t="n">
-        <v>5.11</v>
+        <v>7.12</v>
       </c>
       <c r="C27" s="95" t="n">
         <v>5.11</v>
@@ -9440,7 +9440,7 @@
         </is>
       </c>
       <c r="B28" s="95" t="n">
-        <v>11.06</v>
+        <v>13.45</v>
       </c>
       <c r="C28" s="95" t="n">
         <v>11.06</v>
@@ -9531,13 +9531,13 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="96" t="inlineStr">
+      <c r="A29" s="76" t="inlineStr">
         <is>
           <t>ixic:RS2</t>
         </is>
       </c>
       <c r="B29" s="95" t="n">
-        <v>31.75</v>
+        <v>66.86</v>
       </c>
       <c r="C29" s="95" t="n">
         <v>31.75</v>
@@ -9791,10 +9791,10 @@
         </is>
       </c>
       <c r="B31" s="95" t="n">
-        <v>-0.02</v>
+        <v>0.13</v>
       </c>
       <c r="C31" s="95" t="n">
-        <v>0.4</v>
+        <v>0.03</v>
       </c>
       <c r="D31" s="95" t="n">
         <v>1.82</v>
@@ -9888,10 +9888,10 @@
         </is>
       </c>
       <c r="B32" s="95" t="n">
-        <v>0.8</v>
+        <v>0.95</v>
       </c>
       <c r="C32" s="95" t="n">
-        <v>-0.5</v>
+        <v>-0.87</v>
       </c>
       <c r="D32" s="95" t="n">
         <v>-0.55</v>
@@ -9985,10 +9985,10 @@
         </is>
       </c>
       <c r="B33" s="95" t="n">
-        <v>40.93</v>
+        <v>43.24</v>
       </c>
       <c r="C33" s="95" t="n">
-        <v>41.02</v>
+        <v>39.02</v>
       </c>
       <c r="D33" s="95" t="n">
         <v>45.59</v>
@@ -10687,7 +10687,7 @@
         </is>
       </c>
       <c r="B39" s="95" t="n">
-        <v>-3.54</v>
+        <v>-4.33</v>
       </c>
       <c r="C39" s="95" t="n">
         <v>-4.58</v>
@@ -10784,7 +10784,7 @@
         </is>
       </c>
       <c r="B40" s="95" t="n">
-        <v>4.99</v>
+        <v>4.13</v>
       </c>
       <c r="C40" s="95" t="n">
         <v>2.88</v>
@@ -10875,13 +10875,13 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="76" t="inlineStr">
+      <c r="A41" s="96" t="inlineStr">
         <is>
           <t>sensex:RS10</t>
         </is>
       </c>
       <c r="B41" s="95" t="n">
-        <v>39.17</v>
+        <v>30.62</v>
       </c>
       <c r="C41" s="95" t="n">
         <v>26.76</v>
@@ -10977,9 +10977,9 @@
           <t>fr40:EIDE</t>
         </is>
       </c>
-      <c r="B42" s="92" t="inlineStr">
-        <is>
-          <t>blue</t>
+      <c r="B42" s="91" t="inlineStr">
+        <is>
+          <t>green</t>
         </is>
       </c>
       <c r="C42" s="92" t="inlineStr">
@@ -11135,7 +11135,7 @@
         </is>
       </c>
       <c r="B43" s="95" t="n">
-        <v>-4.17</v>
+        <v>-4.44</v>
       </c>
       <c r="C43" s="95" t="n">
         <v>-4.11</v>
@@ -11232,7 +11232,7 @@
         </is>
       </c>
       <c r="B44" s="95" t="n">
-        <v>-8.67</v>
+        <v>-8.92</v>
       </c>
       <c r="C44" s="95" t="n">
         <v>-9</v>
@@ -11329,7 +11329,7 @@
         </is>
       </c>
       <c r="B45" s="95" t="n">
-        <v>37.74</v>
+        <v>35.01</v>
       </c>
       <c r="C45" s="95" t="n">
         <v>42.3</v>
@@ -11425,9 +11425,9 @@
           <t>dax30:EIDE</t>
         </is>
       </c>
-      <c r="B46" s="92" t="inlineStr">
-        <is>
-          <t>blue</t>
+      <c r="B46" s="91" t="inlineStr">
+        <is>
+          <t>green</t>
         </is>
       </c>
       <c r="C46" s="92" t="inlineStr">
@@ -11583,7 +11583,7 @@
         </is>
       </c>
       <c r="B47" s="95" t="n">
-        <v>3.07</v>
+        <v>2.03</v>
       </c>
       <c r="C47" s="95" t="n">
         <v>3.07</v>
@@ -11680,7 +11680,7 @@
         </is>
       </c>
       <c r="B48" s="95" t="n">
-        <v>3.12</v>
+        <v>3.56</v>
       </c>
       <c r="C48" s="95" t="n">
         <v>3.12</v>
@@ -11777,7 +11777,7 @@
         </is>
       </c>
       <c r="B49" s="95" t="n">
-        <v>48.4</v>
+        <v>41.19</v>
       </c>
       <c r="C49" s="95" t="n">
         <v>48.4</v>
@@ -11870,7 +11870,7 @@
     <row r="51">
       <c r="A51" s="90" t="inlineStr">
         <is>
-          <t>今日买报：ixic:RS2:31.75&lt;=38;vn:RS3:2.81&lt;=25</t>
+          <t>今日买报：us30:RS3:19.64&lt;=25;vn:RS3:2.81&lt;=25;sensex:RS10:30.62&lt;=39</t>
         </is>
       </c>
     </row>

--- a/report_2411.xlsx
+++ b/report_2411.xlsx
@@ -3988,7 +3988,7 @@
         </is>
       </c>
       <c r="B26" s="88" t="n">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="C26" s="88" t="n">
         <v>0.08</v>
@@ -4085,7 +4085,7 @@
         </is>
       </c>
       <c r="B27" s="88" t="n">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="C27" s="88" t="n">
         <v>1.35</v>
@@ -8447,7 +8447,7 @@
         </is>
       </c>
       <c r="B19" s="95" t="n">
-        <v>5.34</v>
+        <v>5.18</v>
       </c>
       <c r="C19" s="95" t="n">
         <v>5.34</v>
@@ -8544,7 +8544,7 @@
         </is>
       </c>
       <c r="B20" s="95" t="n">
-        <v>13.02</v>
+        <v>12.12</v>
       </c>
       <c r="C20" s="95" t="n">
         <v>13.02</v>
@@ -8641,7 +8641,7 @@
         </is>
       </c>
       <c r="B21" s="95" t="n">
-        <v>59.11</v>
+        <v>59.28</v>
       </c>
       <c r="C21" s="95" t="n">
         <v>59.11</v>
@@ -9343,7 +9343,7 @@
         </is>
       </c>
       <c r="B27" s="95" t="n">
-        <v>7.12</v>
+        <v>6.82</v>
       </c>
       <c r="C27" s="95" t="n">
         <v>7.12</v>
@@ -9440,7 +9440,7 @@
         </is>
       </c>
       <c r="B28" s="95" t="n">
-        <v>13.45</v>
+        <v>13.33</v>
       </c>
       <c r="C28" s="95" t="n">
         <v>13.45</v>
@@ -9537,7 +9537,7 @@
         </is>
       </c>
       <c r="B29" s="95" t="n">
-        <v>66.86</v>
+        <v>60.11</v>
       </c>
       <c r="C29" s="95" t="n">
         <v>66.86</v>
@@ -10081,9 +10081,9 @@
           <t>vn:EIDE</t>
         </is>
       </c>
-      <c r="B34" s="92" t="inlineStr">
-        <is>
-          <t>green</t>
+      <c r="B34" s="93" t="inlineStr">
+        <is>
+          <t>blue</t>
         </is>
       </c>
       <c r="C34" s="92" t="inlineStr">
@@ -10239,7 +10239,7 @@
         </is>
       </c>
       <c r="B35" s="95" t="n">
-        <v>-6.24</v>
+        <v>-4.96</v>
       </c>
       <c r="C35" s="95" t="n">
         <v>-6.24</v>
@@ -10336,7 +10336,7 @@
         </is>
       </c>
       <c r="B36" s="95" t="n">
-        <v>-5.85</v>
+        <v>-5.22</v>
       </c>
       <c r="C36" s="95" t="n">
         <v>-5.85</v>
@@ -10427,13 +10427,13 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="96" t="inlineStr">
+      <c r="A37" s="76" t="inlineStr">
         <is>
           <t>vn:RS3</t>
         </is>
       </c>
       <c r="B37" s="95" t="n">
-        <v>2.81</v>
+        <v>41.91</v>
       </c>
       <c r="C37" s="95" t="n">
         <v>2.81</v>
@@ -10977,9 +10977,9 @@
           <t>fr40:EIDE</t>
         </is>
       </c>
-      <c r="B42" s="93" t="inlineStr">
-        <is>
-          <t>blue</t>
+      <c r="B42" s="92" t="inlineStr">
+        <is>
+          <t>green</t>
         </is>
       </c>
       <c r="C42" s="92" t="inlineStr">
@@ -11135,7 +11135,7 @@
         </is>
       </c>
       <c r="B43" s="95" t="n">
-        <v>-4.34</v>
+        <v>-5</v>
       </c>
       <c r="C43" s="95" t="n">
         <v>-4.44</v>
@@ -11232,7 +11232,7 @@
         </is>
       </c>
       <c r="B44" s="95" t="n">
-        <v>-9.460000000000001</v>
+        <v>-10.09</v>
       </c>
       <c r="C44" s="95" t="n">
         <v>-8.92</v>
@@ -11329,7 +11329,7 @@
         </is>
       </c>
       <c r="B45" s="95" t="n">
-        <v>40.17</v>
+        <v>30.76</v>
       </c>
       <c r="C45" s="95" t="n">
         <v>35.01</v>
@@ -11583,7 +11583,7 @@
         </is>
       </c>
       <c r="B47" s="95" t="n">
-        <v>2.03</v>
+        <v>1.18</v>
       </c>
       <c r="C47" s="95" t="n">
         <v>2.03</v>
@@ -11680,7 +11680,7 @@
         </is>
       </c>
       <c r="B48" s="95" t="n">
-        <v>3.56</v>
+        <v>2.31</v>
       </c>
       <c r="C48" s="95" t="n">
         <v>3.56</v>
@@ -11777,7 +11777,7 @@
         </is>
       </c>
       <c r="B49" s="95" t="n">
-        <v>41.19</v>
+        <v>38.25</v>
       </c>
       <c r="C49" s="95" t="n">
         <v>41.19</v>
@@ -11870,7 +11870,7 @@
     <row r="51">
       <c r="A51" s="90" t="inlineStr">
         <is>
-          <t>今日买报：us30:RS3:19.64&lt;=25;vn:RS3:2.81&lt;=25;sensex:RS10:30.62&lt;=39</t>
+          <t>今日买报：us30:RS3:19.64&lt;=25;sensex:RS10:30.62&lt;=39</t>
         </is>
       </c>
     </row>

--- a/report_2411.xlsx
+++ b/report_2411.xlsx
@@ -3988,7 +3988,7 @@
         </is>
       </c>
       <c r="B26" s="88" t="n">
-        <v>-0.03</v>
+        <v>0.06</v>
       </c>
       <c r="C26" s="88" t="n">
         <v>0.23</v>
@@ -4085,7 +4085,7 @@
         </is>
       </c>
       <c r="B27" s="88" t="n">
-        <v>1.71</v>
+        <v>1.81</v>
       </c>
       <c r="C27" s="88" t="n">
         <v>1.6</v>
@@ -8289,9 +8289,9 @@
           <t>us500:EIDE</t>
         </is>
       </c>
-      <c r="B18" s="93" t="inlineStr">
-        <is>
-          <t>blue</t>
+      <c r="B18" s="91" t="inlineStr">
+        <is>
+          <t>red</t>
         </is>
       </c>
       <c r="C18" s="93" t="inlineStr">
@@ -8447,7 +8447,7 @@
         </is>
       </c>
       <c r="B19" s="95" t="n">
-        <v>5.18</v>
+        <v>6.38</v>
       </c>
       <c r="C19" s="95" t="n">
         <v>5.18</v>
@@ -8544,7 +8544,7 @@
         </is>
       </c>
       <c r="B20" s="95" t="n">
-        <v>12.12</v>
+        <v>12.59</v>
       </c>
       <c r="C20" s="95" t="n">
         <v>12.12</v>
@@ -8635,13 +8635,13 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="76" t="inlineStr">
+      <c r="A21" s="94" t="inlineStr">
         <is>
           <t>us500:RS2</t>
         </is>
       </c>
       <c r="B21" s="95" t="n">
-        <v>59.28</v>
+        <v>86.79000000000001</v>
       </c>
       <c r="C21" s="95" t="n">
         <v>59.28</v>
@@ -9343,7 +9343,7 @@
         </is>
       </c>
       <c r="B27" s="95" t="n">
-        <v>6.82</v>
+        <v>8.07</v>
       </c>
       <c r="C27" s="95" t="n">
         <v>6.82</v>
@@ -9440,7 +9440,7 @@
         </is>
       </c>
       <c r="B28" s="95" t="n">
-        <v>13.33</v>
+        <v>12.74</v>
       </c>
       <c r="C28" s="95" t="n">
         <v>13.33</v>
@@ -9537,7 +9537,7 @@
         </is>
       </c>
       <c r="B29" s="95" t="n">
-        <v>60.11</v>
+        <v>62.35</v>
       </c>
       <c r="C29" s="95" t="n">
         <v>60.11</v>
@@ -9633,9 +9633,9 @@
           <t>jp225:EIDE</t>
         </is>
       </c>
-      <c r="B30" s="93" t="inlineStr">
-        <is>
-          <t>blue</t>
+      <c r="B30" s="92" t="inlineStr">
+        <is>
+          <t>green</t>
         </is>
       </c>
       <c r="C30" s="92" t="inlineStr">
@@ -9791,7 +9791,7 @@
         </is>
       </c>
       <c r="B31" s="95" t="n">
-        <v>0.12</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="C31" s="95" t="n">
         <v>0.64</v>
@@ -9888,7 +9888,7 @@
         </is>
       </c>
       <c r="B32" s="95" t="n">
-        <v>-1.52</v>
+        <v>-2.3</v>
       </c>
       <c r="C32" s="95" t="n">
         <v>-0.35</v>
@@ -9985,7 +9985,7 @@
         </is>
       </c>
       <c r="B33" s="95" t="n">
-        <v>41.83</v>
+        <v>36.88</v>
       </c>
       <c r="C33" s="95" t="n">
         <v>42.19</v>
@@ -10687,7 +10687,7 @@
         </is>
       </c>
       <c r="B39" s="95" t="n">
-        <v>-5.58</v>
+        <v>-5.56</v>
       </c>
       <c r="C39" s="95" t="n">
         <v>-4.33</v>
@@ -10784,7 +10784,7 @@
         </is>
       </c>
       <c r="B40" s="95" t="n">
-        <v>4.4</v>
+        <v>4.43</v>
       </c>
       <c r="C40" s="95" t="n">
         <v>4.13</v>
@@ -10881,7 +10881,7 @@
         </is>
       </c>
       <c r="B41" s="95" t="n">
-        <v>27.64</v>
+        <v>27.75</v>
       </c>
       <c r="C41" s="95" t="n">
         <v>30.62</v>
@@ -10977,9 +10977,9 @@
           <t>fr40:EIDE</t>
         </is>
       </c>
-      <c r="B42" s="92" t="inlineStr">
-        <is>
-          <t>green</t>
+      <c r="B42" s="93" t="inlineStr">
+        <is>
+          <t>blue</t>
         </is>
       </c>
       <c r="C42" s="92" t="inlineStr">
@@ -11135,7 +11135,7 @@
         </is>
       </c>
       <c r="B43" s="95" t="n">
-        <v>-5</v>
+        <v>-5.6</v>
       </c>
       <c r="C43" s="95" t="n">
         <v>-5</v>
@@ -11232,7 +11232,7 @@
         </is>
       </c>
       <c r="B44" s="95" t="n">
-        <v>-10.09</v>
+        <v>-10.28</v>
       </c>
       <c r="C44" s="95" t="n">
         <v>-10.09</v>
@@ -11329,7 +11329,7 @@
         </is>
       </c>
       <c r="B45" s="95" t="n">
-        <v>30.76</v>
+        <v>35.43</v>
       </c>
       <c r="C45" s="95" t="n">
         <v>30.76</v>
@@ -11425,9 +11425,9 @@
           <t>dax30:EIDE</t>
         </is>
       </c>
-      <c r="B46" s="92" t="inlineStr">
-        <is>
-          <t>green</t>
+      <c r="B46" s="93" t="inlineStr">
+        <is>
+          <t>blue</t>
         </is>
       </c>
       <c r="C46" s="92" t="inlineStr">
@@ -11583,7 +11583,7 @@
         </is>
       </c>
       <c r="B47" s="95" t="n">
-        <v>0.44</v>
+        <v>1.24</v>
       </c>
       <c r="C47" s="95" t="n">
         <v>1.18</v>
@@ -11680,7 +11680,7 @@
         </is>
       </c>
       <c r="B48" s="95" t="n">
-        <v>1.84</v>
+        <v>2.65</v>
       </c>
       <c r="C48" s="95" t="n">
         <v>2.31</v>
@@ -11777,7 +11777,7 @@
         </is>
       </c>
       <c r="B49" s="95" t="n">
-        <v>37.78</v>
+        <v>49.32</v>
       </c>
       <c r="C49" s="95" t="n">
         <v>38.25</v>
@@ -11870,14 +11870,14 @@
     <row r="51">
       <c r="A51" s="90" t="inlineStr">
         <is>
-          <t>今日买报：sensex:RS10:27.64&lt;=39</t>
+          <t>今日买报：sensex:RS10:27.75&lt;=39</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="90" t="inlineStr">
         <is>
-          <t>今日卖报：sh:RNG60:17.57&gt;=10;kc:RNG60:45.84&gt;=25;kc:RNG120:36.93&gt;=30;cy:RNG60:44.51&gt;=25</t>
+          <t>今日卖报：sh:RNG60:17.57&gt;=10;kc:RNG60:45.84&gt;=25;kc:RNG120:36.93&gt;=30;cy:RNG60:44.51&gt;=25;us500:RS2:86.79&gt;=85</t>
         </is>
       </c>
     </row>

--- a/report_2411.xlsx
+++ b/report_2411.xlsx
@@ -3891,7 +3891,7 @@
         </is>
       </c>
       <c r="B25" s="87" t="n">
-        <v>7.25</v>
+        <v>7.26</v>
       </c>
       <c r="C25" s="87" t="n">
         <v>7.25</v>
@@ -3988,7 +3988,7 @@
         </is>
       </c>
       <c r="B26" s="88" t="n">
-        <v>-0.02</v>
+        <v>0.05</v>
       </c>
       <c r="C26" s="88" t="n">
         <v>0.07000000000000001</v>
@@ -4085,7 +4085,7 @@
         </is>
       </c>
       <c r="B27" s="88" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="C27" s="88" t="n">
         <v>1.82</v>
@@ -8437,7 +8437,7 @@
         </is>
       </c>
       <c r="B19" s="95" t="n">
-        <v>6.38</v>
+        <v>6.75</v>
       </c>
       <c r="C19" s="95" t="n">
         <v>6.38</v>
@@ -8534,7 +8534,7 @@
         </is>
       </c>
       <c r="B20" s="95" t="n">
-        <v>12.59</v>
+        <v>12.81</v>
       </c>
       <c r="C20" s="95" t="n">
         <v>12.59</v>
@@ -8631,7 +8631,7 @@
         </is>
       </c>
       <c r="B21" s="95" t="n">
-        <v>86.79000000000001</v>
+        <v>92.98</v>
       </c>
       <c r="C21" s="95" t="n">
         <v>86.79000000000001</v>
@@ -8883,7 +8883,7 @@
         </is>
       </c>
       <c r="B23" s="95" t="n">
-        <v>6.76</v>
+        <v>7.16</v>
       </c>
       <c r="C23" s="95" t="n">
         <v>6.76</v>
@@ -8980,7 +8980,7 @@
         </is>
       </c>
       <c r="B24" s="95" t="n">
-        <v>13.74</v>
+        <v>14.43</v>
       </c>
       <c r="C24" s="95" t="n">
         <v>13.74</v>
@@ -9071,13 +9071,13 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="76" t="inlineStr">
+      <c r="A25" s="94" t="inlineStr">
         <is>
           <t>us30:RS3</t>
         </is>
       </c>
       <c r="B25" s="95" t="n">
-        <v>76.63</v>
+        <v>87.14</v>
       </c>
       <c r="C25" s="95" t="n">
         <v>76.63</v>
@@ -9329,7 +9329,7 @@
         </is>
       </c>
       <c r="B27" s="95" t="n">
-        <v>8.07</v>
+        <v>8.49</v>
       </c>
       <c r="C27" s="95" t="n">
         <v>8.07</v>
@@ -9426,7 +9426,7 @@
         </is>
       </c>
       <c r="B28" s="95" t="n">
-        <v>12.74</v>
+        <v>12.73</v>
       </c>
       <c r="C28" s="95" t="n">
         <v>12.74</v>
@@ -9523,7 +9523,7 @@
         </is>
       </c>
       <c r="B29" s="95" t="n">
-        <v>62.35</v>
+        <v>75.83</v>
       </c>
       <c r="C29" s="95" t="n">
         <v>62.35</v>
@@ -9775,7 +9775,7 @@
         </is>
       </c>
       <c r="B31" s="95" t="n">
-        <v>-0.44</v>
+        <v>-0.23</v>
       </c>
       <c r="C31" s="95" t="n">
         <v>-0.6899999999999999</v>
@@ -9872,7 +9872,7 @@
         </is>
       </c>
       <c r="B32" s="95" t="n">
-        <v>-1.63</v>
+        <v>-1.43</v>
       </c>
       <c r="C32" s="95" t="n">
         <v>-2.3</v>
@@ -9969,7 +9969,7 @@
         </is>
       </c>
       <c r="B33" s="95" t="n">
-        <v>41.4</v>
+        <v>43.23</v>
       </c>
       <c r="C33" s="95" t="n">
         <v>36.88</v>
@@ -10667,7 +10667,7 @@
         </is>
       </c>
       <c r="B39" s="95" t="n">
-        <v>-3.14</v>
+        <v>-3.18</v>
       </c>
       <c r="C39" s="95" t="n">
         <v>-5.56</v>
@@ -10764,7 +10764,7 @@
         </is>
       </c>
       <c r="B40" s="95" t="n">
-        <v>7.01</v>
+        <v>6.97</v>
       </c>
       <c r="C40" s="95" t="n">
         <v>4.43</v>
@@ -10861,7 +10861,7 @@
         </is>
       </c>
       <c r="B41" s="95" t="n">
-        <v>51.5</v>
+        <v>51.27</v>
       </c>
       <c r="C41" s="95" t="n">
         <v>27.75</v>
@@ -11113,7 +11113,7 @@
         </is>
       </c>
       <c r="B43" s="95" t="n">
-        <v>-5.76</v>
+        <v>-4.93</v>
       </c>
       <c r="C43" s="95" t="n">
         <v>-5.6</v>
@@ -11210,7 +11210,7 @@
         </is>
       </c>
       <c r="B44" s="95" t="n">
-        <v>-10.13</v>
+        <v>-9.33</v>
       </c>
       <c r="C44" s="95" t="n">
         <v>-10.28</v>
@@ -11307,7 +11307,7 @@
         </is>
       </c>
       <c r="B45" s="95" t="n">
-        <v>31.48</v>
+        <v>47.78</v>
       </c>
       <c r="C45" s="95" t="n">
         <v>35.43</v>
@@ -11403,9 +11403,9 @@
           <t>dax30:EIDE</t>
         </is>
       </c>
-      <c r="B46" s="93" t="inlineStr">
-        <is>
-          <t>blue</t>
+      <c r="B46" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
         </is>
       </c>
       <c r="C46" s="93" t="inlineStr">
@@ -11559,7 +11559,7 @@
         </is>
       </c>
       <c r="B47" s="95" t="n">
-        <v>1.14</v>
+        <v>2.2</v>
       </c>
       <c r="C47" s="95" t="n">
         <v>1.24</v>
@@ -11656,7 +11656,7 @@
         </is>
       </c>
       <c r="B48" s="95" t="n">
-        <v>3.05</v>
+        <v>4.12</v>
       </c>
       <c r="C48" s="95" t="n">
         <v>2.65</v>
@@ -11753,7 +11753,7 @@
         </is>
       </c>
       <c r="B49" s="95" t="n">
-        <v>47.66</v>
+        <v>60.04</v>
       </c>
       <c r="C49" s="95" t="n">
         <v>49.32</v>
@@ -11853,7 +11853,7 @@
     <row r="52">
       <c r="A52" s="90" t="inlineStr">
         <is>
-          <t>今日卖报：sh:RNG60:14.37&gt;=10;kc:RNG60:40.15&gt;=25;kc:RNG120:31.91&gt;=30;cy:RNG60:39.59&gt;=25;us500:RS2:86.79&gt;=85</t>
+          <t>今日卖报：sh:RNG60:14.37&gt;=10;kc:RNG60:40.15&gt;=25;kc:RNG120:31.91&gt;=30;cy:RNG60:39.59&gt;=25;us500:RS2:92.98&gt;=85;us30:RS3:87.14&gt;=85</t>
         </is>
       </c>
     </row>

--- a/report_2411.xlsx
+++ b/report_2411.xlsx
@@ -3988,7 +3988,7 @@
         </is>
       </c>
       <c r="B26" s="88" t="n">
-        <v>-0.14</v>
+        <v>-0.16</v>
       </c>
       <c r="C26" s="88" t="n">
         <v>0.05</v>
@@ -4085,7 +4085,7 @@
         </is>
       </c>
       <c r="B27" s="88" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="C27" s="88" t="n">
         <v>1.75</v>
@@ -8447,7 +8447,7 @@
         </is>
       </c>
       <c r="B19" s="95" t="n">
-        <v>6.75</v>
+        <v>6</v>
       </c>
       <c r="C19" s="95" t="n">
         <v>6.75</v>
@@ -8544,7 +8544,7 @@
         </is>
       </c>
       <c r="B20" s="95" t="n">
-        <v>12.81</v>
+        <v>11.83</v>
       </c>
       <c r="C20" s="95" t="n">
         <v>12.81</v>
@@ -8641,7 +8641,7 @@
         </is>
       </c>
       <c r="B21" s="95" t="n">
-        <v>92.98</v>
+        <v>96.14</v>
       </c>
       <c r="C21" s="95" t="n">
         <v>92.98</v>
@@ -8895,7 +8895,7 @@
         </is>
       </c>
       <c r="B23" s="95" t="n">
-        <v>7.16</v>
+        <v>7.64</v>
       </c>
       <c r="C23" s="95" t="n">
         <v>7.16</v>
@@ -8992,7 +8992,7 @@
         </is>
       </c>
       <c r="B24" s="95" t="n">
-        <v>14.43</v>
+        <v>15.28</v>
       </c>
       <c r="C24" s="95" t="n">
         <v>14.43</v>
@@ -9089,7 +9089,7 @@
         </is>
       </c>
       <c r="B25" s="95" t="n">
-        <v>87.14</v>
+        <v>92.42</v>
       </c>
       <c r="C25" s="95" t="n">
         <v>87.14</v>
@@ -9185,9 +9185,9 @@
           <t>ixic:EIDE</t>
         </is>
       </c>
-      <c r="B26" s="93" t="inlineStr">
-        <is>
-          <t>blue</t>
+      <c r="B26" s="92" t="inlineStr">
+        <is>
+          <t>red</t>
         </is>
       </c>
       <c r="C26" s="93" t="inlineStr">
@@ -9343,7 +9343,7 @@
         </is>
       </c>
       <c r="B27" s="95" t="n">
-        <v>8.49</v>
+        <v>7.57</v>
       </c>
       <c r="C27" s="95" t="n">
         <v>8.49</v>
@@ -9440,7 +9440,7 @@
         </is>
       </c>
       <c r="B28" s="95" t="n">
-        <v>12.73</v>
+        <v>10.86</v>
       </c>
       <c r="C28" s="95" t="n">
         <v>12.73</v>
@@ -9537,7 +9537,7 @@
         </is>
       </c>
       <c r="B29" s="95" t="n">
-        <v>75.83</v>
+        <v>88.88</v>
       </c>
       <c r="C29" s="95" t="n">
         <v>75.83</v>
@@ -10687,7 +10687,7 @@
         </is>
       </c>
       <c r="B39" s="95" t="n">
-        <v>-2.11</v>
+        <v>-2.05</v>
       </c>
       <c r="C39" s="95" t="n">
         <v>-3.18</v>
@@ -10784,7 +10784,7 @@
         </is>
       </c>
       <c r="B40" s="95" t="n">
-        <v>4.7</v>
+        <v>4.76</v>
       </c>
       <c r="C40" s="95" t="n">
         <v>6.97</v>
@@ -10881,7 +10881,7 @@
         </is>
       </c>
       <c r="B41" s="95" t="n">
-        <v>58.5</v>
+        <v>58.81</v>
       </c>
       <c r="C41" s="95" t="n">
         <v>51.27</v>
@@ -11135,7 +11135,7 @@
         </is>
       </c>
       <c r="B43" s="95" t="n">
-        <v>-4.93</v>
+        <v>-5.09</v>
       </c>
       <c r="C43" s="95" t="n">
         <v>-4.93</v>
@@ -11232,7 +11232,7 @@
         </is>
       </c>
       <c r="B44" s="95" t="n">
-        <v>-9.33</v>
+        <v>-8.06</v>
       </c>
       <c r="C44" s="95" t="n">
         <v>-9.33</v>
@@ -11329,7 +11329,7 @@
         </is>
       </c>
       <c r="B45" s="95" t="n">
-        <v>47.78</v>
+        <v>48.51</v>
       </c>
       <c r="C45" s="95" t="n">
         <v>47.78</v>
@@ -11583,7 +11583,7 @@
         </is>
       </c>
       <c r="B47" s="95" t="n">
-        <v>2.38</v>
+        <v>2.51</v>
       </c>
       <c r="C47" s="95" t="n">
         <v>2.2</v>
@@ -11680,7 +11680,7 @@
         </is>
       </c>
       <c r="B48" s="95" t="n">
-        <v>4.79</v>
+        <v>4.92</v>
       </c>
       <c r="C48" s="95" t="n">
         <v>4.12</v>
@@ -11777,7 +11777,7 @@
         </is>
       </c>
       <c r="B49" s="95" t="n">
-        <v>63.14</v>
+        <v>64.28</v>
       </c>
       <c r="C49" s="95" t="n">
         <v>60.04</v>
@@ -11877,7 +11877,7 @@
     <row r="52">
       <c r="A52" s="90" t="inlineStr">
         <is>
-          <t>今日卖报：sh:RNG60:14.57&gt;=10;kc:RNG60:39.73&gt;=25;kc:RNG120:30.45&gt;=30;cy:RNG60:40.64&gt;=25;us500:RS2:92.98&gt;=85;us30:RS3:87.14&gt;=85</t>
+          <t>今日卖报：sh:RNG60:14.57&gt;=10;kc:RNG60:39.73&gt;=25;kc:RNG120:30.45&gt;=30;cy:RNG60:40.64&gt;=25;us500:RS2:96.14&gt;=85;us30:RS3:92.42&gt;=85</t>
         </is>
       </c>
     </row>

--- a/report_2411.xlsx
+++ b/report_2411.xlsx
@@ -3988,7 +3988,7 @@
         </is>
       </c>
       <c r="B26" s="88" t="n">
-        <v>0.22</v>
+        <v>0.15</v>
       </c>
       <c r="C26" s="88" t="n">
         <v>-0.16</v>
@@ -4085,7 +4085,7 @@
         </is>
       </c>
       <c r="B27" s="88" t="n">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="C27" s="88" t="n">
         <v>1.45</v>
@@ -8447,7 +8447,7 @@
         </is>
       </c>
       <c r="B19" s="95" t="n">
-        <v>6</v>
+        <v>8.91</v>
       </c>
       <c r="C19" s="95" t="n">
         <v>6</v>
@@ -8544,7 +8544,7 @@
         </is>
       </c>
       <c r="B20" s="95" t="n">
-        <v>11.83</v>
+        <v>12.49</v>
       </c>
       <c r="C20" s="95" t="n">
         <v>11.83</v>
@@ -8641,7 +8641,7 @@
         </is>
       </c>
       <c r="B21" s="95" t="n">
-        <v>96.14</v>
+        <v>98.58</v>
       </c>
       <c r="C21" s="95" t="n">
         <v>96.14</v>
@@ -8895,7 +8895,7 @@
         </is>
       </c>
       <c r="B23" s="95" t="n">
-        <v>7.64</v>
+        <v>9.58</v>
       </c>
       <c r="C23" s="95" t="n">
         <v>7.64</v>
@@ -8992,7 +8992,7 @@
         </is>
       </c>
       <c r="B24" s="95" t="n">
-        <v>15.28</v>
+        <v>15.36</v>
       </c>
       <c r="C24" s="95" t="n">
         <v>15.28</v>
@@ -9089,7 +9089,7 @@
         </is>
       </c>
       <c r="B25" s="95" t="n">
-        <v>92.42</v>
+        <v>93.54000000000001</v>
       </c>
       <c r="C25" s="95" t="n">
         <v>92.42</v>
@@ -9343,7 +9343,7 @@
         </is>
       </c>
       <c r="B27" s="95" t="n">
-        <v>7.57</v>
+        <v>11.89</v>
       </c>
       <c r="C27" s="95" t="n">
         <v>7.57</v>
@@ -9440,7 +9440,7 @@
         </is>
       </c>
       <c r="B28" s="95" t="n">
-        <v>10.86</v>
+        <v>11.65</v>
       </c>
       <c r="C28" s="95" t="n">
         <v>10.86</v>
@@ -9531,13 +9531,13 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="76" t="inlineStr">
+      <c r="A29" s="94" t="inlineStr">
         <is>
           <t>ixic:RS2</t>
         </is>
       </c>
       <c r="B29" s="95" t="n">
-        <v>88.88</v>
+        <v>96.84</v>
       </c>
       <c r="C29" s="95" t="n">
         <v>88.88</v>
@@ -9633,9 +9633,9 @@
           <t>jp225:EIDE</t>
         </is>
       </c>
-      <c r="B30" s="91" t="inlineStr">
-        <is>
-          <t>green</t>
+      <c r="B30" s="93" t="inlineStr">
+        <is>
+          <t>blue</t>
         </is>
       </c>
       <c r="C30" s="92" t="inlineStr">
@@ -9791,7 +9791,7 @@
         </is>
       </c>
       <c r="B31" s="95" t="n">
-        <v>-1.12</v>
+        <v>-0.53</v>
       </c>
       <c r="C31" s="95" t="n">
         <v>1.09</v>
@@ -9888,7 +9888,7 @@
         </is>
       </c>
       <c r="B32" s="95" t="n">
-        <v>-1.26</v>
+        <v>-0.68</v>
       </c>
       <c r="C32" s="95" t="n">
         <v>0.75</v>
@@ -9985,7 +9985,7 @@
         </is>
       </c>
       <c r="B33" s="95" t="n">
-        <v>43.42</v>
+        <v>46.95</v>
       </c>
       <c r="C33" s="95" t="n">
         <v>53.39</v>
@@ -10687,7 +10687,7 @@
         </is>
       </c>
       <c r="B39" s="95" t="n">
-        <v>-2.63</v>
+        <v>-2.59</v>
       </c>
       <c r="C39" s="95" t="n">
         <v>-2.05</v>
@@ -10784,7 +10784,7 @@
         </is>
       </c>
       <c r="B40" s="95" t="n">
-        <v>10.96</v>
+        <v>10.99</v>
       </c>
       <c r="C40" s="95" t="n">
         <v>4.76</v>
@@ -10881,7 +10881,7 @@
         </is>
       </c>
       <c r="B41" s="95" t="n">
-        <v>57.48</v>
+        <v>57.75</v>
       </c>
       <c r="C41" s="95" t="n">
         <v>58.81</v>
@@ -11135,7 +11135,7 @@
         </is>
       </c>
       <c r="B43" s="95" t="n">
-        <v>-4.99</v>
+        <v>-5.02</v>
       </c>
       <c r="C43" s="95" t="n">
         <v>-5.09</v>
@@ -11232,7 +11232,7 @@
         </is>
       </c>
       <c r="B44" s="95" t="n">
-        <v>-7.61</v>
+        <v>-7.63</v>
       </c>
       <c r="C44" s="95" t="n">
         <v>-8.06</v>
@@ -11329,7 +11329,7 @@
         </is>
       </c>
       <c r="B45" s="95" t="n">
-        <v>33.96</v>
+        <v>33.57</v>
       </c>
       <c r="C45" s="95" t="n">
         <v>48.51</v>
@@ -11583,7 +11583,7 @@
         </is>
       </c>
       <c r="B47" s="95" t="n">
-        <v>2.51</v>
+        <v>2.93</v>
       </c>
       <c r="C47" s="95" t="n">
         <v>2.51</v>
@@ -11680,7 +11680,7 @@
         </is>
       </c>
       <c r="B48" s="95" t="n">
-        <v>4.92</v>
+        <v>5.04</v>
       </c>
       <c r="C48" s="95" t="n">
         <v>4.92</v>
@@ -11777,7 +11777,7 @@
         </is>
       </c>
       <c r="B49" s="95" t="n">
-        <v>64.28</v>
+        <v>55.01</v>
       </c>
       <c r="C49" s="95" t="n">
         <v>64.28</v>
@@ -11877,7 +11877,7 @@
     <row r="52">
       <c r="A52" s="90" t="inlineStr">
         <is>
-          <t>今日卖报：sh:RNG60:14.2&gt;=10;kc:RNG60:38.76&gt;=25;cy:RNG60:38.99&gt;=25;us500:RS2:96.14&gt;=85;us30:RS3:92.42&gt;=85</t>
+          <t>今日卖报：sh:RNG60:14.2&gt;=10;kc:RNG60:38.76&gt;=25;cy:RNG60:38.99&gt;=25;us500:RS2:98.58&gt;=85;us30:RS3:93.54&gt;=85;ixic:RS2:96.84&gt;=96</t>
         </is>
       </c>
     </row>

--- a/report_2411.xlsx
+++ b/report_2411.xlsx
@@ -3890,7 +3890,7 @@
         </is>
       </c>
       <c r="B25" s="87" t="n">
-        <v>7.26</v>
+        <v>7.24</v>
       </c>
       <c r="C25" s="87" t="n">
         <v>7.26</v>
@@ -3987,7 +3987,7 @@
         </is>
       </c>
       <c r="B26" s="88" t="n">
-        <v>0.01</v>
+        <v>-0.18</v>
       </c>
       <c r="C26" s="88" t="n">
         <v>0.15</v>
@@ -4084,7 +4084,7 @@
         </is>
       </c>
       <c r="B27" s="88" t="n">
-        <v>1.86</v>
+        <v>1.66</v>
       </c>
       <c r="C27" s="88" t="n">
         <v>1.62</v>
@@ -8288,9 +8288,9 @@
           <t>us500:EIDE</t>
         </is>
       </c>
-      <c r="B18" s="93" t="inlineStr">
-        <is>
-          <t>red</t>
+      <c r="B18" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
         </is>
       </c>
       <c r="C18" s="93" t="inlineStr">
@@ -8446,7 +8446,7 @@
         </is>
       </c>
       <c r="B19" s="95" t="n">
-        <v>8.91</v>
+        <v>8.67</v>
       </c>
       <c r="C19" s="95" t="n">
         <v>8.91</v>
@@ -8543,7 +8543,7 @@
         </is>
       </c>
       <c r="B20" s="95" t="n">
-        <v>12.49</v>
+        <v>12.19</v>
       </c>
       <c r="C20" s="95" t="n">
         <v>12.49</v>
@@ -8634,13 +8634,13 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="94" t="inlineStr">
+      <c r="A21" s="76" t="inlineStr">
         <is>
           <t>us500:RS2</t>
         </is>
       </c>
       <c r="B21" s="95" t="n">
-        <v>98.58</v>
+        <v>53.48</v>
       </c>
       <c r="C21" s="95" t="n">
         <v>98.58</v>
@@ -8736,9 +8736,9 @@
           <t>us30:EIDE</t>
         </is>
       </c>
-      <c r="B22" s="93" t="inlineStr">
-        <is>
-          <t>red</t>
+      <c r="B22" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
         </is>
       </c>
       <c r="C22" s="93" t="inlineStr">
@@ -8894,7 +8894,7 @@
         </is>
       </c>
       <c r="B23" s="95" t="n">
-        <v>9.58</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="C23" s="95" t="n">
         <v>9.58</v>
@@ -8991,7 +8991,7 @@
         </is>
       </c>
       <c r="B24" s="95" t="n">
-        <v>15.36</v>
+        <v>15.27</v>
       </c>
       <c r="C24" s="95" t="n">
         <v>15.36</v>
@@ -9082,13 +9082,13 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="94" t="inlineStr">
+      <c r="A25" s="76" t="inlineStr">
         <is>
           <t>us30:RS3</t>
         </is>
       </c>
       <c r="B25" s="95" t="n">
-        <v>93.54000000000001</v>
+        <v>74.98999999999999</v>
       </c>
       <c r="C25" s="95" t="n">
         <v>93.54000000000001</v>
@@ -9184,9 +9184,9 @@
           <t>ixic:EIDE</t>
         </is>
       </c>
-      <c r="B26" s="93" t="inlineStr">
-        <is>
-          <t>red</t>
+      <c r="B26" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
         </is>
       </c>
       <c r="C26" s="93" t="inlineStr">
@@ -9342,7 +9342,7 @@
         </is>
       </c>
       <c r="B27" s="95" t="n">
-        <v>11.89</v>
+        <v>11.57</v>
       </c>
       <c r="C27" s="95" t="n">
         <v>11.89</v>
@@ -9439,7 +9439,7 @@
         </is>
       </c>
       <c r="B28" s="95" t="n">
-        <v>11.65</v>
+        <v>11.25</v>
       </c>
       <c r="C28" s="95" t="n">
         <v>11.65</v>
@@ -9530,13 +9530,13 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="94" t="inlineStr">
+      <c r="A29" s="76" t="inlineStr">
         <is>
           <t>ixic:RS2</t>
         </is>
       </c>
       <c r="B29" s="95" t="n">
-        <v>96.84</v>
+        <v>40.96</v>
       </c>
       <c r="C29" s="95" t="n">
         <v>96.84</v>
@@ -9632,9 +9632,9 @@
           <t>jp225:EIDE</t>
         </is>
       </c>
-      <c r="B30" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
+      <c r="B30" s="92" t="inlineStr">
+        <is>
+          <t>green</t>
         </is>
       </c>
       <c r="C30" s="91" t="inlineStr">
@@ -9790,7 +9790,7 @@
         </is>
       </c>
       <c r="B31" s="95" t="n">
-        <v>-1.02</v>
+        <v>-1.46</v>
       </c>
       <c r="C31" s="95" t="n">
         <v>-0.53</v>
@@ -9887,7 +9887,7 @@
         </is>
       </c>
       <c r="B32" s="95" t="n">
-        <v>-0.98</v>
+        <v>-1.42</v>
       </c>
       <c r="C32" s="95" t="n">
         <v>-0.68</v>
@@ -9984,7 +9984,7 @@
         </is>
       </c>
       <c r="B33" s="95" t="n">
-        <v>44.51</v>
+        <v>41.8</v>
       </c>
       <c r="C33" s="95" t="n">
         <v>46.95</v>
@@ -11134,7 +11134,7 @@
         </is>
       </c>
       <c r="B43" s="95" t="n">
-        <v>-5.02</v>
+        <v>-4.77</v>
       </c>
       <c r="C43" s="95" t="n">
         <v>-5.02</v>
@@ -11231,7 +11231,7 @@
         </is>
       </c>
       <c r="B44" s="95" t="n">
-        <v>-9.41</v>
+        <v>-9.18</v>
       </c>
       <c r="C44" s="95" t="n">
         <v>-7.63</v>
@@ -11328,7 +11328,7 @@
         </is>
       </c>
       <c r="B45" s="95" t="n">
-        <v>23.53</v>
+        <v>25.53</v>
       </c>
       <c r="C45" s="95" t="n">
         <v>33.57</v>
@@ -11582,7 +11582,7 @@
         </is>
       </c>
       <c r="B47" s="95" t="n">
-        <v>3.46</v>
+        <v>3.6</v>
       </c>
       <c r="C47" s="95" t="n">
         <v>2.93</v>
@@ -11679,7 +11679,7 @@
         </is>
       </c>
       <c r="B48" s="95" t="n">
-        <v>3.24</v>
+        <v>3.39</v>
       </c>
       <c r="C48" s="95" t="n">
         <v>5.04</v>
@@ -11776,7 +11776,7 @@
         </is>
       </c>
       <c r="B49" s="95" t="n">
-        <v>50.11</v>
+        <v>52.18</v>
       </c>
       <c r="C49" s="95" t="n">
         <v>55.01</v>
@@ -11876,7 +11876,7 @@
     <row r="52">
       <c r="A52" s="90" t="inlineStr">
         <is>
-          <t>今日卖报：sh:RNG60:15.91&gt;=10;kc:RNG60:44.46&gt;=25;kc:RNG120:32.66&gt;=30;cy:RNG60:42.93&gt;=25;us500:RS2:98.58&gt;=85;us30:RS3:93.54&gt;=85;ixic:RS2:96.84&gt;=96</t>
+          <t>今日卖报：sh:RNG60:15.91&gt;=10;kc:RNG60:44.46&gt;=25;kc:RNG120:32.66&gt;=30;cy:RNG60:42.93&gt;=25</t>
         </is>
       </c>
     </row>

--- a/report_2411.xlsx
+++ b/report_2411.xlsx
@@ -3890,7 +3890,7 @@
         </is>
       </c>
       <c r="B25" s="87" t="n">
-        <v>7.26</v>
+        <v>7.25</v>
       </c>
       <c r="C25" s="87" t="n">
         <v>7.24</v>
@@ -3987,7 +3987,7 @@
         </is>
       </c>
       <c r="B26" s="88" t="n">
-        <v>0.18</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="C26" s="88" t="n">
         <v>-0.18</v>
@@ -4084,7 +4084,7 @@
         </is>
       </c>
       <c r="B27" s="88" t="n">
-        <v>1.93</v>
+        <v>1.81</v>
       </c>
       <c r="C27" s="88" t="n">
         <v>1.66</v>
@@ -10238,7 +10238,7 @@
         </is>
       </c>
       <c r="B35" s="95" t="n">
-        <v>-1.92</v>
+        <v>-2.06</v>
       </c>
       <c r="C35" s="95" t="n">
         <v>-2.65</v>
@@ -10335,7 +10335,7 @@
         </is>
       </c>
       <c r="B36" s="95" t="n">
-        <v>-4.34</v>
+        <v>-4.47</v>
       </c>
       <c r="C36" s="95" t="n">
         <v>-3.3</v>
@@ -10426,13 +10426,13 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="94" t="inlineStr">
+      <c r="A37" s="76" t="inlineStr">
         <is>
           <t>vn:RS3</t>
         </is>
       </c>
       <c r="B37" s="95" t="n">
-        <v>85.87</v>
+        <v>83.34999999999999</v>
       </c>
       <c r="C37" s="95" t="n">
         <v>83.11</v>
@@ -10686,7 +10686,7 @@
         </is>
       </c>
       <c r="B39" s="95" t="n">
-        <v>-4.19</v>
+        <v>-4.26</v>
       </c>
       <c r="C39" s="95" t="n">
         <v>-2.59</v>
@@ -10783,7 +10783,7 @@
         </is>
       </c>
       <c r="B40" s="95" t="n">
-        <v>5.36</v>
+        <v>5.29</v>
       </c>
       <c r="C40" s="95" t="n">
         <v>7.87</v>
@@ -10880,7 +10880,7 @@
         </is>
       </c>
       <c r="B41" s="95" t="n">
-        <v>48.45</v>
+        <v>48.01</v>
       </c>
       <c r="C41" s="95" t="n">
         <v>59.51</v>
@@ -10976,9 +10976,9 @@
           <t>fr40:EIDE</t>
         </is>
       </c>
-      <c r="B42" s="92" t="inlineStr">
-        <is>
-          <t>green</t>
+      <c r="B42" s="91" t="inlineStr">
+        <is>
+          <t>blue</t>
         </is>
       </c>
       <c r="C42" s="92" t="inlineStr">
@@ -11134,7 +11134,7 @@
         </is>
       </c>
       <c r="B43" s="95" t="n">
-        <v>-4.77</v>
+        <v>-3.4</v>
       </c>
       <c r="C43" s="95" t="n">
         <v>-4.77</v>
@@ -11231,7 +11231,7 @@
         </is>
       </c>
       <c r="B44" s="95" t="n">
-        <v>-9.18</v>
+        <v>-6.86</v>
       </c>
       <c r="C44" s="95" t="n">
         <v>-9.18</v>
@@ -11328,7 +11328,7 @@
         </is>
       </c>
       <c r="B45" s="95" t="n">
-        <v>25.53</v>
+        <v>38.48</v>
       </c>
       <c r="C45" s="95" t="n">
         <v>25.53</v>
@@ -11424,9 +11424,9 @@
           <t>dax30:EIDE</t>
         </is>
       </c>
-      <c r="B46" s="91" t="inlineStr">
-        <is>
-          <t>blue</t>
+      <c r="B46" s="93" t="inlineStr">
+        <is>
+          <t>red</t>
         </is>
       </c>
       <c r="C46" s="91" t="inlineStr">
@@ -11582,7 +11582,7 @@
         </is>
       </c>
       <c r="B47" s="95" t="n">
-        <v>3.6</v>
+        <v>4.56</v>
       </c>
       <c r="C47" s="95" t="n">
         <v>3.6</v>
@@ -11679,7 +11679,7 @@
         </is>
       </c>
       <c r="B48" s="95" t="n">
-        <v>3.39</v>
+        <v>6.34</v>
       </c>
       <c r="C48" s="95" t="n">
         <v>3.39</v>
@@ -11776,7 +11776,7 @@
         </is>
       </c>
       <c r="B49" s="95" t="n">
-        <v>52.18</v>
+        <v>62.96</v>
       </c>
       <c r="C49" s="95" t="n">
         <v>52.18</v>
@@ -11876,7 +11876,7 @@
     <row r="52">
       <c r="A52" s="90" t="inlineStr">
         <is>
-          <t>今日卖报：sh:RNG60:15.69&gt;=10;kc:RNG60:45.87&gt;=25;kc:RNG120:31.08&gt;=30;cy:RNG60:41.75&gt;=25;vn:RS3:85.87&gt;=85</t>
+          <t>今日卖报：sh:RNG60:15.69&gt;=10;kc:RNG60:45.87&gt;=25;kc:RNG120:31.08&gt;=30;cy:RNG60:41.75&gt;=25</t>
         </is>
       </c>
     </row>

--- a/report_2411.xlsx
+++ b/report_2411.xlsx
@@ -3987,7 +3987,7 @@
         </is>
       </c>
       <c r="B26" s="88" t="n">
-        <v>-0.04</v>
+        <v>-0.02</v>
       </c>
       <c r="C26" s="88" t="n">
         <v>0.07000000000000001</v>
@@ -4084,7 +4084,7 @@
         </is>
       </c>
       <c r="B27" s="88" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="C27" s="88" t="n">
         <v>1.81</v>
@@ -8280,9 +8280,9 @@
           <t>us500:EIDE</t>
         </is>
       </c>
-      <c r="B18" s="92" t="inlineStr">
-        <is>
-          <t>blue</t>
+      <c r="B18" s="91" t="inlineStr">
+        <is>
+          <t>red</t>
         </is>
       </c>
       <c r="C18" s="92" t="inlineStr">
@@ -8436,7 +8436,7 @@
         </is>
       </c>
       <c r="B19" s="95" t="n">
-        <v>8.67</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="C19" s="95" t="n">
         <v>8.67</v>
@@ -8533,7 +8533,7 @@
         </is>
       </c>
       <c r="B20" s="95" t="n">
-        <v>12.19</v>
+        <v>12.53</v>
       </c>
       <c r="C20" s="95" t="n">
         <v>12.19</v>
@@ -8630,7 +8630,7 @@
         </is>
       </c>
       <c r="B21" s="95" t="n">
-        <v>53.48</v>
+        <v>80.16</v>
       </c>
       <c r="C21" s="95" t="n">
         <v>53.48</v>
@@ -8726,9 +8726,9 @@
           <t>us30:EIDE</t>
         </is>
       </c>
-      <c r="B22" s="92" t="inlineStr">
-        <is>
-          <t>blue</t>
+      <c r="B22" s="91" t="inlineStr">
+        <is>
+          <t>red</t>
         </is>
       </c>
       <c r="C22" s="92" t="inlineStr">
@@ -8876,13 +8876,13 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="76" t="inlineStr">
+      <c r="A23" s="94" t="inlineStr">
         <is>
           <t>us30:RNG60</t>
         </is>
       </c>
       <c r="B23" s="95" t="n">
-        <v>9.140000000000001</v>
+        <v>10.19</v>
       </c>
       <c r="C23" s="95" t="n">
         <v>9.140000000000001</v>
@@ -8979,7 +8979,7 @@
         </is>
       </c>
       <c r="B24" s="95" t="n">
-        <v>15.27</v>
+        <v>15.55</v>
       </c>
       <c r="C24" s="95" t="n">
         <v>15.27</v>
@@ -9076,7 +9076,7 @@
         </is>
       </c>
       <c r="B25" s="95" t="n">
-        <v>74.98999999999999</v>
+        <v>82.20999999999999</v>
       </c>
       <c r="C25" s="95" t="n">
         <v>74.98999999999999</v>
@@ -9172,9 +9172,9 @@
           <t>ixic:EIDE</t>
         </is>
       </c>
-      <c r="B26" s="92" t="inlineStr">
-        <is>
-          <t>blue</t>
+      <c r="B26" s="91" t="inlineStr">
+        <is>
+          <t>red</t>
         </is>
       </c>
       <c r="C26" s="92" t="inlineStr">
@@ -9328,7 +9328,7 @@
         </is>
       </c>
       <c r="B27" s="95" t="n">
-        <v>11.57</v>
+        <v>12.21</v>
       </c>
       <c r="C27" s="95" t="n">
         <v>11.57</v>
@@ -9425,7 +9425,7 @@
         </is>
       </c>
       <c r="B28" s="95" t="n">
-        <v>11.25</v>
+        <v>11.78</v>
       </c>
       <c r="C28" s="95" t="n">
         <v>11.25</v>
@@ -9522,7 +9522,7 @@
         </is>
       </c>
       <c r="B29" s="95" t="n">
-        <v>40.96</v>
+        <v>77.28</v>
       </c>
       <c r="C29" s="95" t="n">
         <v>40.96</v>
@@ -10956,9 +10956,9 @@
           <t>fr40:EIDE</t>
         </is>
       </c>
-      <c r="B42" s="93" t="inlineStr">
-        <is>
-          <t>green</t>
+      <c r="B42" s="92" t="inlineStr">
+        <is>
+          <t>blue</t>
         </is>
       </c>
       <c r="C42" s="92" t="inlineStr">
@@ -11112,7 +11112,7 @@
         </is>
       </c>
       <c r="B43" s="95" t="n">
-        <v>-2.78</v>
+        <v>-1.59</v>
       </c>
       <c r="C43" s="95" t="n">
         <v>-3.4</v>
@@ -11209,7 +11209,7 @@
         </is>
       </c>
       <c r="B44" s="95" t="n">
-        <v>-4.74</v>
+        <v>-3.57</v>
       </c>
       <c r="C44" s="95" t="n">
         <v>-6.86</v>
@@ -11306,7 +11306,7 @@
         </is>
       </c>
       <c r="B45" s="95" t="n">
-        <v>32.36</v>
+        <v>53.93</v>
       </c>
       <c r="C45" s="95" t="n">
         <v>38.48</v>
@@ -11558,7 +11558,7 @@
         </is>
       </c>
       <c r="B47" s="95" t="n">
-        <v>6.07</v>
+        <v>7.24</v>
       </c>
       <c r="C47" s="95" t="n">
         <v>4.57</v>
@@ -11655,7 +11655,7 @@
         </is>
       </c>
       <c r="B48" s="95" t="n">
-        <v>7.84</v>
+        <v>9.02</v>
       </c>
       <c r="C48" s="95" t="n">
         <v>6.35</v>
@@ -11752,7 +11752,7 @@
         </is>
       </c>
       <c r="B49" s="95" t="n">
-        <v>61.81</v>
+        <v>72.36</v>
       </c>
       <c r="C49" s="95" t="n">
         <v>63.1</v>
@@ -11852,7 +11852,7 @@
     <row r="52">
       <c r="A52" s="90" t="inlineStr">
         <is>
-          <t>今日卖报：sh:RNG60:17.23&gt;=10;sh:RS3:67.49&gt;=66;kc:RNG60:50.08&gt;=25;kc:RNG120:33.67&gt;=30;cy:RNG60:45.22&gt;=25;vn:RS3:92.78&gt;=85</t>
+          <t>今日卖报：sh:RNG60:17.23&gt;=10;sh:RS3:67.49&gt;=66;kc:RNG60:50.08&gt;=25;kc:RNG120:33.67&gt;=30;cy:RNG60:45.22&gt;=25;us30:RNG60:10.19&gt;=10;vn:RS3:92.78&gt;=85</t>
         </is>
       </c>
     </row>
